--- a/published/01_Equity_Global.xlsx
+++ b/published/01_Equity_Global.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Global_Funders" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Global_Funders'!$A$1:$L$685</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Global_Funders'!$A$1:$K$685</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L685"/>
+  <dimension ref="A1:K685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -448,8 +448,7 @@
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="50" customWidth="1" min="11" max="11"/>
-    <col width="42" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,11 +504,6 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Source / Verification</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -561,12 +555,7 @@
           <t>Series C-Z</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://luxorcap.com/team)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -615,12 +604,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://alven.co/team)</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -669,12 +653,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://whitestarcapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -723,12 +702,7 @@
           <t>Pre-Seed</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://antler.co/team)</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -777,12 +751,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://pico.partners/team)</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -831,12 +800,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://aleph.vc/team)</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -885,12 +849,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://pitango.com/team)</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -939,12 +898,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://viola-group.com/team)</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -993,12 +947,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://vertexventures.co.il/team)</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1047,12 +996,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://tlv.partners/team)</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1101,12 +1045,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://upwest.vc/team)</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1155,12 +1094,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://lool.vc/team)</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1209,12 +1143,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://glilotcapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1263,12 +1192,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://angularventures.com/team)</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1317,12 +1241,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://ignitetech.com/team)</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1371,12 +1290,7 @@
           <t>Series C-Z</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://founderscircle.com/team)</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1425,12 +1339,7 @@
           <t>Series B-Z</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://g2vp.com/team)</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1479,12 +1388,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://peakxv.com/team)</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1533,12 +1437,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://firstminute.capital/team)</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1587,12 +1486,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>https://agfunder.com/about-us/</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1641,12 +1535,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.s2ginvestments.com/team</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1695,12 +1584,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>https://pontifaxagtech.com/investment-team</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1749,12 +1633,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>https://paineschwartz.com/about-us/the-firm/</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1803,12 +1682,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>https://astanor.com/about-us/</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1857,12 +1731,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>https://bluehorizon.com/about/</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1911,12 +1780,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>https://www.eitfood.eu/about-us</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1965,12 +1829,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>https://a16zcrypto.com/about/</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2019,12 +1878,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>https://faction.vc#team</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2073,12 +1927,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>https://ambergroup.io/</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2127,12 +1976,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>https://fenbushi.vc/our-team-of-professionals/</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2181,12 +2025,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>https://ngc.fund/about-ngc</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2235,12 +2074,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>https://gbv.capital/whoweare</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2289,12 +2123,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>https://www.signum.capital/about/</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2343,12 +2172,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>https://morningstar.ventures/#team</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2397,12 +2221,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kucoin.com/about-us</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2451,12 +2270,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>https://okx.com/en-us/learn/category/blog</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2505,12 +2319,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/o6kLbiG7a7ZXTziVA</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2559,12 +2368,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>https://krustuniverse.com#p2</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2613,12 +2417,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>https://a16z.com/team/</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2667,12 +2466,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>https://griffingp.com/ggp-team/</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2721,12 +2515,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>https://www.scout.vc/team</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2775,12 +2564,7 @@
           <t>Early Stage</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>https://www.decisivepoint.com/team</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2829,12 +2613,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>https://contrary.com/team</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2883,12 +2662,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>https://www.hustlefund.vc/team</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2937,12 +2711,7 @@
           <t>Growth / Late Stage</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tcv.com/contact</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2991,12 +2760,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>https://www.abingworth.com/team</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3045,12 +2809,7 @@
           <t>Series A-B</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>https://actoncapital.com/team</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3099,12 +2858,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>https://seedcamp.com/our-team/</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3153,12 +2907,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>https://www.future.africa/about-us</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3207,12 +2956,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>https://www.venturesplatform.com/team</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3261,12 +3005,7 @@
           <t>Seed / Early Stage</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>https://www.echovc.com/team</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3315,12 +3054,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>https://jvpvc.com/team/</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3369,12 +3103,7 @@
           <t>Early Stage / Growth</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.iris.vc/team</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3423,12 +3152,7 @@
           <t>Seed / Pre-Series A</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>https://www.launchafrica.vc/team</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3477,12 +3201,7 @@
           <t>Early Stage</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>https://1789.vc</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3531,12 +3250,7 @@
           <t>Early Stage / Growth</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>https://www.paladincapitalgroup.com/team/</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3585,12 +3299,7 @@
           <t>Early Stage</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>https://www.razorsedge.com/team/</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3639,12 +3348,7 @@
           <t>Growth / Debt / Equity</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>https://enlightenment-cap.com/team/</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3693,12 +3397,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>https://www.moonshotscapital.com/team/</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3747,12 +3446,7 @@
           <t>Early Stage</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>https://www.silentvc.com/team/</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3801,12 +3495,7 @@
           <t>Early Stage / Growth</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>https://www.almazcapital.com/team</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3855,12 +3544,7 @@
           <t>Seed / Early Stage</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>https://www.archventure.com/team/</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3909,12 +3593,7 @@
           <t>Early Stage</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>https://www.flagshippioneering.com/people</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3963,12 +3642,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>https://foundercollective.com/team</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4017,12 +3691,7 @@
           <t>Early Stage</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>https://www.usvp.com/team</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4071,12 +3740,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>https://www.jafco.co.jp/english/team/</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4125,12 +3789,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vertexholdings.com/team/</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4179,12 +3838,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>https://www.questventures.com/corporate/about/</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4233,12 +3887,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>https://www.healthcap.eu/team</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4287,12 +3936,7 @@
           <t>Seed / EIS</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>https://www.syndicateroom.com/about/team</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4341,12 +3985,7 @@
           <t>Early Stage</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>https://www.marqueventures.com/team</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4395,12 +4034,7 @@
           <t>Early Stage</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>https://www.snowpointventures.com/team</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4449,12 +4083,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>https://www.canary.com.br/team</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4503,12 +4132,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>https://maya-capital.com/team</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4557,12 +4181,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>https://onevc.vc/team</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4611,12 +4230,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>https://savannah.vc/team</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4665,12 +4279,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>https://gaingels.com/about/</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4719,12 +4328,7 @@
           <t>Early Stage / Growth</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>https://headline.com/team</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4773,12 +4377,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nvp.com/team</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4827,12 +4426,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>https://www.versantventures.com/team</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4881,12 +4475,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>https://www.oakvc.com/team/</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4935,12 +4524,7 @@
           <t>Growth / License</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>https://www.intellectualventures.com/who-we-are/leadership</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -4989,12 +4573,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mayfield.com/team</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5043,12 +4622,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>https://www.blumbergcapital.com/team</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5097,12 +4671,7 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>https://capitalg.com/team</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5151,12 +4720,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>https://3one4capital.com/team</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5205,12 +4769,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dagventures.com/team</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5259,12 +4818,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>https://uncorkcapital.com/team</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5313,12 +4867,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>https://svangel.com/team</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5367,12 +4916,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>https://tenayacapital.com/team</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5421,12 +4965,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>https://www.thirdrockventures.com/team</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5475,12 +5014,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>https://www.vivocapital.com/team</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -5529,12 +5063,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>https://www.waldenintl.com/team</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5583,12 +5112,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>https://www.dncapital.com/team</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -5637,12 +5161,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>http://www.genesispartners.com/team</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5691,12 +5210,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>https://www.infinity-cp.com/team</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5745,12 +5259,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>https://iidf.ru/en/team/</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5799,12 +5308,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>https://www.mercia.co.uk/team</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5853,12 +5357,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>https://www.newfundcap.com/team</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5907,12 +5406,7 @@
           <t>Seed / Growth</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>https://www.novafounders.com/team</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -5961,12 +5455,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>https://www.oxfordscienceenterprises.com/team</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6015,12 +5504,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>http://www.portongroup.com</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -6069,12 +5553,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>https://www.5ycap.com/en/team</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6123,12 +5602,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>http://www.addorcapital.com</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6177,12 +5651,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>http://www.casstar.com.cn</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6231,12 +5700,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>http://www.chinareform.com</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6285,12 +5749,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t>http://www.costonecapital.com</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6339,12 +5798,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>http://www.cowincapital.com</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6393,12 +5847,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K110" s="2" t="inlineStr">
-        <is>
-          <t>http://www.ebellcap.com</t>
-        </is>
-      </c>
-      <c r="L110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6447,12 +5896,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>http://www.szvc.com.cn</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6501,12 +5945,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>http://www.gaorongvc.com</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6555,12 +5994,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>https://www.graniteasia.com/team</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -6609,12 +6043,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hongshan.com/team</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6663,12 +6092,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>https://idgcapital.com/team</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6717,12 +6141,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>https://www.jic-vgi.jp/english/team/</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6771,12 +6190,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>http://www.k2vc.com</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -6825,12 +6239,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K118" s="2" t="inlineStr">
-        <is>
-          <t>http://www.lanchivc.com</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6879,12 +6288,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>http://www.miracleplus.com</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -6933,12 +6337,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>http://www.nlvc.com</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6987,12 +6386,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>http://www.ofc.com.cn</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -7041,12 +6435,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>http://www.oriza.com.cn</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7095,12 +6484,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>http://www.plumventures.cn</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -7149,12 +6533,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K124" s="2" t="inlineStr">
-        <is>
-          <t>http://www.shvc.com.cn</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7203,12 +6582,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>http://www.szvc.com.cn</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -7257,12 +6631,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K126" s="2" t="inlineStr">
-        <is>
-          <t>http://www.szhti.com.cn</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7311,12 +6680,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>http://www.shunwei.com</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -7365,12 +6729,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K128" s="2" t="inlineStr">
-        <is>
-          <t>http://www.sinovationventures.com</t>
-        </is>
-      </c>
-      <c r="L128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7419,12 +6778,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>http://www.sourcecodecap.com</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -7473,12 +6827,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K130" s="2" t="inlineStr">
-        <is>
-          <t>http://www.stic.co.kr</t>
-        </is>
-      </c>
-      <c r="L130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7527,12 +6876,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>http://www.tiantucapital.com</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -7581,12 +6925,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>http://www.zwcpartners.com</t>
-        </is>
-      </c>
-      <c r="L132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7635,12 +6974,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>https://human.capital</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -7689,12 +7023,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>https://bedrock.com</t>
-        </is>
-      </c>
-      <c r="L134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7743,12 +7072,7 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>https://piedmontcapital.com</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -7797,12 +7121,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hbmhealthcare.com/en/about-us/team</t>
-        </is>
-      </c>
-      <c r="L136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7851,12 +7170,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>https://www.atv.com/team</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -7905,12 +7219,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K138" s="2" t="inlineStr">
-        <is>
-          <t>https://www.atlasventure.com/team</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7959,12 +7268,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>http://www.augustcap.com/team</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -8013,12 +7317,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K140" s="2" t="inlineStr">
-        <is>
-          <t>http://www.austinventures.com</t>
-        </is>
-      </c>
-      <c r="L140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8067,12 +7366,7 @@
           <t>Growth</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>https://www.bondcap.com</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -8121,12 +7415,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K142" s="2" t="inlineStr">
-        <is>
-          <t>http://www.legendcapital.com.cn</t>
-        </is>
-      </c>
-      <c r="L142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8175,12 +7464,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>http://www.kaitaicapital.com</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -8229,12 +7513,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K144" s="2" t="inlineStr">
-        <is>
-          <t>https://www.socialcapital.com/about</t>
-        </is>
-      </c>
-      <c r="L144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8283,12 +7562,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>https://www.paradigm.xyz/team</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -8337,12 +7611,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K146" s="2" t="inlineStr">
-        <is>
-          <t>https://polychain.capital</t>
-        </is>
-      </c>
-      <c r="L146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8391,12 +7660,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>https://homebrew.co/team</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -8445,12 +7709,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K148" s="2" t="inlineStr">
-        <is>
-          <t>https://cowboy.vc/team</t>
-        </is>
-      </c>
-      <c r="L148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8499,12 +7758,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>https://menlovc.com/team</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -8553,12 +7807,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K150" s="2" t="inlineStr">
-        <is>
-          <t>https://www.shv.com</t>
-        </is>
-      </c>
-      <c r="L150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8607,12 +7856,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>https://entreecap.com/team</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -8661,12 +7905,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K152" s="2" t="inlineStr">
-        <is>
-          <t>https://cyberstarts.com/team</t>
-        </is>
-      </c>
-      <c r="L152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8715,12 +7954,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>https://greenoaks.com</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -8769,12 +8003,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>https://squadra.vc/team</t>
-        </is>
-      </c>
-      <c r="L154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8823,12 +8052,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>https://www.firstin.vc/team</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -8877,12 +8101,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gulatech.com/team</t>
-        </is>
-      </c>
-      <c r="L156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8931,12 +8150,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>https://tfxcap.com/team</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -8985,12 +8199,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t>https://veteranventures.us/team</t>
-        </is>
-      </c>
-      <c r="L158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9039,12 +8248,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>https://starburst.aero/team</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -9093,12 +8297,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K160" s="2" t="inlineStr">
-        <is>
-          <t>https://www.embedded.vc/team</t>
-        </is>
-      </c>
-      <c r="L160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9147,12 +8346,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>https://www.gradient.com/team</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -9201,12 +8395,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K162" s="2" t="inlineStr">
-        <is>
-          <t>https://section32.com/team</t>
-        </is>
-      </c>
-      <c r="L162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9255,12 +8444,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>https://playground.vc/team</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -9309,12 +8493,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K164" s="2" t="inlineStr">
-        <is>
-          <t>https://radical.vc/team</t>
-        </is>
-      </c>
-      <c r="L164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9363,12 +8542,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>https://zettavp.com/team</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -9417,12 +8591,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K166" s="2" t="inlineStr">
-        <is>
-          <t>https://acrewcapital.com/team</t>
-        </is>
-      </c>
-      <c r="L166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9471,12 +8640,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>https://www.unusual.vc/team</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -9525,12 +8689,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K168" s="2" t="inlineStr">
-        <is>
-          <t>https://susaventures.com/team</t>
-        </is>
-      </c>
-      <c r="L168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9579,12 +8738,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>https://haystack.vc/team</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -9633,12 +8787,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K170" s="2" t="inlineStr">
-        <is>
-          <t>https://645ventures.com/team</t>
-        </is>
-      </c>
-      <c r="L170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9687,12 +8836,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>https://equal.vc/team</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -9741,12 +8885,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K172" s="2" t="inlineStr">
-        <is>
-          <t>https://boldstart.vc/team</t>
-        </is>
-      </c>
-      <c r="L172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9795,12 +8934,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>https://www.work-bench.com/team</t>
-        </is>
-      </c>
-      <c r="L173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -9849,12 +8983,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K174" s="2" t="inlineStr">
-        <is>
-          <t>https://www.heavybit.com/team</t>
-        </is>
-      </c>
-      <c r="L174" s="2" t="inlineStr"/>
+      <c r="K174" s="2" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9903,12 +9032,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>https://theory.vc/team</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -9957,12 +9081,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K176" s="2" t="inlineStr">
-        <is>
-          <t>https://www.conviction.com/team</t>
-        </is>
-      </c>
-      <c r="L176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10011,12 +9130,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>https://www.aixventures.com/team</t>
-        </is>
-      </c>
-      <c r="L177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -10065,12 +9179,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K178" s="2" t="inlineStr">
-        <is>
-          <t>https://www.southparkcommons.com/team</t>
-        </is>
-      </c>
-      <c r="L178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10119,12 +9228,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>https://www.btv.vc/team</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -10173,12 +9277,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K180" s="2" t="inlineStr">
-        <is>
-          <t>https://flourishventures.com/team</t>
-        </is>
-      </c>
-      <c r="L180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10227,12 +9326,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>https://ttvcapital.com/team</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -10281,12 +9375,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K182" s="2" t="inlineStr">
-        <is>
-          <t>https://www.luge.vc/team</t>
-        </is>
-      </c>
-      <c r="L182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -10335,12 +9424,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>https://www.canapi.com/team</t>
-        </is>
-      </c>
-      <c r="L183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -10389,12 +9473,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K184" s="2" t="inlineStr">
-        <is>
-          <t>https://www.arborventures.com/team</t>
-        </is>
-      </c>
-      <c r="L184" s="2" t="inlineStr"/>
+      <c r="K184" s="2" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10443,12 +9522,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>https://www.ingressivecapital.com/team</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -10497,12 +9571,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K186" s="2" t="inlineStr">
-        <is>
-          <t>https://www.4dicapital.com/team</t>
-        </is>
-      </c>
-      <c r="L186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -10551,12 +9620,7 @@
           <t>Series A-B</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>https://www.knifecap.com/team</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -10605,12 +9669,7 @@
           <t>Series A-B</t>
         </is>
       </c>
-      <c r="K188" s="2" t="inlineStr">
-        <is>
-          <t>https://vkav.vc/team</t>
-        </is>
-      </c>
-      <c r="L188" s="2" t="inlineStr"/>
+      <c r="K188" s="2" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -10659,12 +9718,7 @@
           <t>Pre-Seed</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>https://www.microtraction.com/team</t>
-        </is>
-      </c>
-      <c r="L189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -10713,12 +9767,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K190" s="2" t="inlineStr">
-        <is>
-          <t>https://kalonvp.com/team</t>
-        </is>
-      </c>
-      <c r="L190" s="2" t="inlineStr"/>
+      <c r="K190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10767,12 +9816,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>https://savant.co.za/team</t>
-        </is>
-      </c>
-      <c r="L191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -10821,12 +9865,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K192" s="2" t="inlineStr">
-        <is>
-          <t>https://adlevocapital.com/team</t>
-        </is>
-      </c>
-      <c r="L192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10875,12 +9914,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>https://valorcapitalgroup.com/team</t>
-        </is>
-      </c>
-      <c r="L193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -10929,12 +9963,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K194" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dila.vc/team</t>
-        </is>
-      </c>
-      <c r="L194" s="2" t="inlineStr"/>
+      <c r="K194" s="2" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10983,12 +10012,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>https://wollef.vc/team</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -11037,12 +10061,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K196" s="2" t="inlineStr">
-        <is>
-          <t>https://nazca.vc/team</t>
-        </is>
-      </c>
-      <c r="L196" s="2" t="inlineStr"/>
+      <c r="K196" s="2" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -11091,12 +10110,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>https://daluscapital.com/team</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -11145,12 +10159,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K198" s="2" t="inlineStr">
-        <is>
-          <t>https://angelventures.vc/team</t>
-        </is>
-      </c>
-      <c r="L198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -11199,12 +10208,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>https://www.ignia.mx/team</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -11253,12 +10257,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K200" s="2" t="inlineStr">
-        <is>
-          <t>https://wavemaker.vc/team</t>
-        </is>
-      </c>
-      <c r="L200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -11307,12 +10306,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>https://intudo.vc/team</t>
-        </is>
-      </c>
-      <c r="L201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -11361,12 +10355,7 @@
           <t>Series A-B</t>
         </is>
       </c>
-      <c r="K202" s="2" t="inlineStr">
-        <is>
-          <t>https://patamar.com/team</t>
-        </is>
-      </c>
-      <c r="L202" s="2" t="inlineStr"/>
+      <c r="K202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -11415,12 +10404,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>https://vickersventure.com/team</t>
-        </is>
-      </c>
-      <c r="L203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -11469,12 +10453,7 @@
           <t>Series A-B</t>
         </is>
       </c>
-      <c r="K204" s="2" t="inlineStr">
-        <is>
-          <t>https://www.qualgro.com/team</t>
-        </is>
-      </c>
-      <c r="L204" s="2" t="inlineStr"/>
+      <c r="K204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -11523,12 +10502,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>https://www.boozallen.com/about/ventures.html</t>
-        </is>
-      </c>
-      <c r="L205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -11577,12 +10551,7 @@
           <t>Strategic</t>
         </is>
       </c>
-      <c r="K206" s="2" t="inlineStr">
-        <is>
-          <t>https://www.northropgrumman.com/who-we-are/leadership/</t>
-        </is>
-      </c>
-      <c r="L206" s="2" t="inlineStr"/>
+      <c r="K206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -11631,12 +10600,7 @@
           <t>Series B-Z</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>https://www.generalatlantic.com/team</t>
-        </is>
-      </c>
-      <c r="L207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -11685,12 +10649,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K208" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cvc.com/about-us/leadership</t>
-        </is>
-      </c>
-      <c r="L208" s="2" t="inlineStr"/>
+      <c r="K208" s="2" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -11739,12 +10698,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>https://www.apax.com/team</t>
-        </is>
-      </c>
-      <c r="L209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -11793,12 +10747,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K210" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bridgepoint.eu/team</t>
-        </is>
-      </c>
-      <c r="L210" s="2" t="inlineStr"/>
+      <c r="K210" s="2" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -11847,12 +10796,7 @@
           <t>Series C-Z</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>https://www.gic.com.sg/about-us/leadership</t>
-        </is>
-      </c>
-      <c r="L211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -11901,12 +10845,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K212" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cppinvestments.com/about-us/our-leadership/</t>
-        </is>
-      </c>
-      <c r="L212" s="2" t="inlineStr"/>
+      <c r="K212" s="2" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -11955,12 +10894,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>https://www.otpp.com/en-ca/about-us/our-leadership/</t>
-        </is>
-      </c>
-      <c r="L213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -12009,12 +10943,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K214" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cdpq.com/en/about-us/leadership</t>
-        </is>
-      </c>
-      <c r="L214" s="2" t="inlineStr"/>
+      <c r="K214" s="2" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12063,12 +10992,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>https://www.futurefund.gov.au/about-us/our-people/leadership-team</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -12117,12 +11041,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K216" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nbim.no/en/the-fund/governance/leader-group/</t>
-        </is>
-      </c>
-      <c r="L216" s="2" t="inlineStr"/>
+      <c r="K216" s="2" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -12171,12 +11090,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>https://www.khazanah.com.my/about-us/leadership/</t>
-        </is>
-      </c>
-      <c r="L217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -12225,12 +11139,7 @@
           <t>Series C-Z</t>
         </is>
       </c>
-      <c r="K218" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bailliegifford.com/en/usa/about-us/our-people/</t>
-        </is>
-      </c>
-      <c r="L218" s="2" t="inlineStr"/>
+      <c r="K218" s="2" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -12279,12 +11188,7 @@
           <t>Series C-Z</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>https://ark-invest.com/our-team</t>
-        </is>
-      </c>
-      <c r="L219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -12333,12 +11237,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K220" s="2" t="inlineStr">
-        <is>
-          <t>https://www.essencevc.com/team</t>
-        </is>
-      </c>
-      <c r="L220" s="2" t="inlineStr"/>
+      <c r="K220" s="2" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -12387,12 +11286,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>https://character.vc/team</t>
-        </is>
-      </c>
-      <c r="L221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -12441,12 +11335,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K222" s="2" t="inlineStr">
-        <is>
-          <t>https://footwork.vc/team</t>
-        </is>
-      </c>
-      <c r="L222" s="2" t="inlineStr"/>
+      <c r="K222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -12495,12 +11384,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>https://www.standardcrypto.vc/team</t>
-        </is>
-      </c>
-      <c r="L223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -12549,12 +11433,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K224" s="2" t="inlineStr">
-        <is>
-          <t>https://www.haun.co/team</t>
-        </is>
-      </c>
-      <c r="L224" s="2" t="inlineStr"/>
+      <c r="K224" s="2" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -12603,12 +11482,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>https://www.electriccapital.com/team</t>
-        </is>
-      </c>
-      <c r="L225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -12657,12 +11531,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K226" s="2" t="inlineStr">
-        <is>
-          <t>https://distributedglobal.com/team</t>
-        </is>
-      </c>
-      <c r="L226" s="2" t="inlineStr"/>
+      <c r="K226" s="2" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -12711,12 +11580,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>https://dragonfly.xyz/team</t>
-        </is>
-      </c>
-      <c r="L227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -12765,12 +11629,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K228" s="2" t="inlineStr">
-        <is>
-          <t>https://robotventures.com/team</t>
-        </is>
-      </c>
-      <c r="L228" s="2" t="inlineStr"/>
+      <c r="K228" s="2" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -12819,12 +11678,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>https://1kx.network/team</t>
-        </is>
-      </c>
-      <c r="L229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -12873,12 +11727,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K230" s="2" t="inlineStr">
-        <is>
-          <t>https://www.chapterone.com/team</t>
-        </is>
-      </c>
-      <c r="L230" s="2" t="inlineStr"/>
+      <c r="K230" s="2" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -12927,12 +11776,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>https://kindredventures.com/team</t>
-        </is>
-      </c>
-      <c r="L231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -12981,12 +11825,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K232" s="2" t="inlineStr">
-        <is>
-          <t>https://sovereignscapital.com/team</t>
-        </is>
-      </c>
-      <c r="L232" s="2" t="inlineStr"/>
+      <c r="K232" s="2" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -13035,12 +11874,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>https://patron.xyz/team</t>
-        </is>
-      </c>
-      <c r="L233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -13089,12 +11923,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K234" s="2" t="inlineStr">
-        <is>
-          <t>https://makersfund.com/team</t>
-        </is>
-      </c>
-      <c r="L234" s="2" t="inlineStr"/>
+      <c r="K234" s="2" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -13143,12 +11972,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t>https://www.playventures.vc/team</t>
-        </is>
-      </c>
-      <c r="L235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -13197,12 +12021,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K236" s="2" t="inlineStr">
-        <is>
-          <t>https://vgames.vc/team</t>
-        </is>
-      </c>
-      <c r="L236" s="2" t="inlineStr"/>
+      <c r="K236" s="2" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -13251,12 +12070,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>https://www.galaxyinteractive.io/team</t>
-        </is>
-      </c>
-      <c r="L237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -13305,12 +12119,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K238" s="2" t="inlineStr">
-        <is>
-          <t>https://lvp.vc/team</t>
-        </is>
-      </c>
-      <c r="L238" s="2" t="inlineStr"/>
+      <c r="K238" s="2" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -13359,12 +12168,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t>https://initialcapital.com/team</t>
-        </is>
-      </c>
-      <c r="L239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -13413,12 +12217,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K240" s="2" t="inlineStr">
-        <is>
-          <t>https://shima.capital/team</t>
-        </is>
-      </c>
-      <c r="L240" s="2" t="inlineStr"/>
+      <c r="K240" s="2" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -13467,12 +12266,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t>https://jumpcrypto.com/team</t>
-        </is>
-      </c>
-      <c r="L241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -13521,12 +12315,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K242" s="2" t="inlineStr">
-        <is>
-          <t>https://www.wintermute.com/about</t>
-        </is>
-      </c>
-      <c r="L242" s="2" t="inlineStr"/>
+      <c r="K242" s="2" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -13575,12 +12364,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t>https://www.spartangroup.io/team</t>
-        </is>
-      </c>
-      <c r="L243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -13629,12 +12413,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K244" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.hoxtonventures.com/team)</t>
-        </is>
-      </c>
-      <c r="L244" s="2" t="inlineStr"/>
+      <c r="K244" s="2" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -13683,12 +12462,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://octopusventures.com/our-team/)</t>
-        </is>
-      </c>
-      <c r="L245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -13737,12 +12511,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K246" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.notion.vc/team)</t>
-        </is>
-      </c>
-      <c r="L246" s="2" t="inlineStr"/>
+      <c r="K246" s="2" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -13791,12 +12560,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://dawncapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -13845,12 +12609,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K248" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://northzone.com/team)</t>
-        </is>
-      </c>
-      <c r="L248" s="2" t="inlineStr"/>
+      <c r="K248" s="2" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -13899,12 +12658,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://eqtventures.com/team)</t>
-        </is>
-      </c>
-      <c r="L249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -13953,12 +12707,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K250" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://creandum.com/team)</t>
-        </is>
-      </c>
-      <c r="L250" s="2" t="inlineStr"/>
+      <c r="K250" s="2" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -14007,12 +12756,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://cherry.vc/team)</t>
-        </is>
-      </c>
-      <c r="L251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -14061,12 +12805,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K252" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.pointnine.com/team)</t>
-        </is>
-      </c>
-      <c r="L252" s="2" t="inlineStr"/>
+      <c r="K252" s="2" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -14115,12 +12854,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.hvcapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L253" t="inlineStr"/>
+      <c r="K253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -14169,12 +12903,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K254" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://earlybird.com)</t>
-        </is>
-      </c>
-      <c r="L254" s="2" t="inlineStr"/>
+      <c r="K254" s="2" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -14223,12 +12952,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.targetglobal.vc)</t>
-        </is>
-      </c>
-      <c r="L255" t="inlineStr"/>
+      <c r="K255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -14277,12 +13001,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K256" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.lakestar.com)</t>
-        </is>
-      </c>
-      <c r="L256" s="2" t="inlineStr"/>
+      <c r="K256" s="2" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -14331,12 +13050,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://kimaventures.com)</t>
-        </is>
-      </c>
-      <c r="L257" t="inlineStr"/>
+      <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -14385,12 +13099,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K258" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://alven.co)</t>
-        </is>
-      </c>
-      <c r="L258" s="2" t="inlineStr"/>
+      <c r="K258" s="2" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -14439,12 +13148,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.elaia.com/team)</t>
-        </is>
-      </c>
-      <c r="L259" t="inlineStr"/>
+      <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -14493,12 +13197,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K260" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.serena.vc)</t>
-        </is>
-      </c>
-      <c r="L260" s="2" t="inlineStr"/>
+      <c r="K260" s="2" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -14547,12 +13246,7 @@
           <t>Grant / Debt / Equity</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.bpifrance.fr/nous-connaitre)</t>
-        </is>
-      </c>
-      <c r="L261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -14601,12 +13295,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K262" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.htgf.de/en/team/)</t>
-        </is>
-      </c>
-      <c r="L262" s="2" t="inlineStr"/>
+      <c r="K262" s="2" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -14655,12 +13344,7 @@
           <t>Grant</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.ukri.org/who-we-are/innovate-uk/)</t>
-        </is>
-      </c>
-      <c r="L263" t="inlineStr"/>
+      <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -14709,12 +13393,7 @@
           <t>Grant</t>
         </is>
       </c>
-      <c r="K264" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.nsf.gov/staff)</t>
-        </is>
-      </c>
-      <c r="L264" s="2" t="inlineStr"/>
+      <c r="K264" s="2" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -14763,12 +13442,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>https://8vc.com/team</t>
-        </is>
-      </c>
-      <c r="L265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -14817,12 +13491,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K266" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dcvc.com/team</t>
-        </is>
-      </c>
-      <c r="L266" s="2" t="inlineStr"/>
+      <c r="K266" s="2" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -14871,12 +13540,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>https://www.nfx.com/team</t>
-        </is>
-      </c>
-      <c r="L267" t="inlineStr"/>
+      <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -14925,12 +13589,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K268" s="2" t="inlineStr">
-        <is>
-          <t>https://obvious.com/team/</t>
-        </is>
-      </c>
-      <c r="L268" s="2" t="inlineStr"/>
+      <c r="K268" s="2" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -14979,12 +13638,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>https://www.felicis.com/team</t>
-        </is>
-      </c>
-      <c r="L269" t="inlineStr"/>
+      <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -15033,12 +13687,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K270" s="2" t="inlineStr">
-        <is>
-          <t>https://initialized.com/team</t>
-        </is>
-      </c>
-      <c r="L270" s="2" t="inlineStr"/>
+      <c r="K270" s="2" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -15087,12 +13736,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>https://www.crv.com/team</t>
-        </is>
-      </c>
-      <c r="L271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -15141,12 +13785,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K272" s="2" t="inlineStr">
-        <is>
-          <t>https://www.redpoint.com/team/</t>
-        </is>
-      </c>
-      <c r="L272" s="2" t="inlineStr"/>
+      <c r="K272" s="2" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -15195,12 +13834,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>https://sparkcapital.com/team</t>
-        </is>
-      </c>
-      <c r="L273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -15249,12 +13883,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K274" s="2" t="inlineStr">
-        <is>
-          <t>https://ribbitcap.com/team/</t>
-        </is>
-      </c>
-      <c r="L274" s="2" t="inlineStr"/>
+      <c r="K274" s="2" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -15303,12 +13932,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t>https://qedinvestors.com/team</t>
-        </is>
-      </c>
-      <c r="L275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -15357,12 +13981,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K276" s="2" t="inlineStr">
-        <is>
-          <t>https://www.anthemis.com/team/</t>
-        </is>
-      </c>
-      <c r="L276" s="2" t="inlineStr"/>
+      <c r="K276" s="2" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -15411,12 +14030,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t>https://portagevc.com/team/</t>
-        </is>
-      </c>
-      <c r="L277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -15465,12 +14079,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K278" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nyca.com/team</t>
-        </is>
-      </c>
-      <c r="L278" s="2" t="inlineStr"/>
+      <c r="K278" s="2" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -15519,12 +14128,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>https://www.fintech.io/team</t>
-        </is>
-      </c>
-      <c r="L279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -15573,12 +14177,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K280" s="2" t="inlineStr">
-        <is>
-          <t>https://www.canvas.vc/team</t>
-        </is>
-      </c>
-      <c r="L280" s="2" t="inlineStr"/>
+      <c r="K280" s="2" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -15627,12 +14226,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t>https://foundationcapital.com/team/</t>
-        </is>
-      </c>
-      <c r="L281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -15681,12 +14275,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K282" s="2" t="inlineStr">
-        <is>
-          <t>https://www.canaan.com/team</t>
-        </is>
-      </c>
-      <c r="L282" s="2" t="inlineStr"/>
+      <c r="K282" s="2" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -15735,12 +14324,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t>https://matrixpartners.com/team</t>
-        </is>
-      </c>
-      <c r="L283" t="inlineStr"/>
+      <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -15789,12 +14373,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K284" s="2" t="inlineStr">
-        <is>
-          <t>https://www.usv.com/team/</t>
-        </is>
-      </c>
-      <c r="L284" s="2" t="inlineStr"/>
+      <c r="K284" s="2" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -15843,12 +14422,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t>https://thrivecap.com/team</t>
-        </is>
-      </c>
-      <c r="L285" t="inlineStr"/>
+      <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -15897,12 +14471,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K286" s="2" t="inlineStr">
-        <is>
-          <t>https://firstmarkcap.com/team/</t>
-        </is>
-      </c>
-      <c r="L286" s="2" t="inlineStr"/>
+      <c r="K286" s="2" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -15951,12 +14520,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t>https://www.rre.com/team</t>
-        </is>
-      </c>
-      <c r="L287" t="inlineStr"/>
+      <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -16005,12 +14569,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K288" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lererhippeau.com/team</t>
-        </is>
-      </c>
-      <c r="L288" s="2" t="inlineStr"/>
+      <c r="K288" s="2" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -16059,12 +14618,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>https://greycroft.com/team/</t>
-        </is>
-      </c>
-      <c r="L289" t="inlineStr"/>
+      <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -16113,12 +14667,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K290" s="2" t="inlineStr">
-        <is>
-          <t>https://eniac.vc/team</t>
-        </is>
-      </c>
-      <c r="L290" s="2" t="inlineStr"/>
+      <c r="K290" s="2" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -16167,12 +14716,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t>https://bowerycap.com/team</t>
-        </is>
-      </c>
-      <c r="L291" t="inlineStr"/>
+      <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -16221,12 +14765,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K292" s="2" t="inlineStr">
-        <is>
-          <t>https://boxgroup.com/team</t>
-        </is>
-      </c>
-      <c r="L292" s="2" t="inlineStr"/>
+      <c r="K292" s="2" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -16275,12 +14814,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t>https://slow.co/team</t>
-        </is>
-      </c>
-      <c r="L293" t="inlineStr"/>
+      <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -16329,12 +14863,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K294" s="2" t="inlineStr">
-        <is>
-          <t>https://www.harrisonmetal.com/about</t>
-        </is>
-      </c>
-      <c r="L294" s="2" t="inlineStr"/>
+      <c r="K294" s="2" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -16383,12 +14912,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t>https://baselinev.com/</t>
-        </is>
-      </c>
-      <c r="L295" t="inlineStr"/>
+      <c r="K295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -16437,12 +14961,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K296" s="2" t="inlineStr">
-        <is>
-          <t>https://www.floodgate.com/team</t>
-        </is>
-      </c>
-      <c r="L296" s="2" t="inlineStr"/>
+      <c r="K296" s="2" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -16491,12 +15010,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t>https://forerunnerventures.com/team/</t>
-        </is>
-      </c>
-      <c r="L297" t="inlineStr"/>
+      <c r="K297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -16545,12 +15059,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K298" s="2" t="inlineStr">
-        <is>
-          <t>https://shastaventures.com/team/</t>
-        </is>
-      </c>
-      <c r="L298" s="2" t="inlineStr"/>
+      <c r="K298" s="2" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -16599,12 +15108,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t>https://www.venrock.com/team/</t>
-        </is>
-      </c>
-      <c r="L299" t="inlineStr"/>
+      <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -16653,12 +15157,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K300" s="2" t="inlineStr">
-        <is>
-          <t>https://www.scalevp.com/team</t>
-        </is>
-      </c>
-      <c r="L300" s="2" t="inlineStr"/>
+      <c r="K300" s="2" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -16707,12 +15206,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>https://www.meritechcapital.com/team</t>
-        </is>
-      </c>
-      <c r="L301" t="inlineStr"/>
+      <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -16761,12 +15255,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K302" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ivp.com/team/</t>
-        </is>
-      </c>
-      <c r="L302" s="2" t="inlineStr"/>
+      <c r="K302" s="2" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -16815,12 +15304,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t>https://sapphireventures.com/team/</t>
-        </is>
-      </c>
-      <c r="L303" t="inlineStr"/>
+      <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -16869,12 +15353,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K304" s="2" t="inlineStr">
-        <is>
-          <t>https://iconiqcapital.com/team</t>
-        </is>
-      </c>
-      <c r="L304" s="2" t="inlineStr"/>
+      <c r="K304" s="2" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -16923,12 +15402,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t>https://addition.com/</t>
-        </is>
-      </c>
-      <c r="L305" t="inlineStr"/>
+      <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -16977,12 +15451,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K306" s="2" t="inlineStr">
-        <is>
-          <t>https://www.dragoneer.com/team/</t>
-        </is>
-      </c>
-      <c r="L306" s="2" t="inlineStr"/>
+      <c r="K306" s="2" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -17031,12 +15500,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t>https://altimeter.com/team/</t>
-        </is>
-      </c>
-      <c r="L307" t="inlineStr"/>
+      <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -17085,12 +15549,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K308" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ggvc.com/team/</t>
-        </is>
-      </c>
-      <c r="L308" s="2" t="inlineStr"/>
+      <c r="K308" s="2" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -17139,12 +15598,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t>https://www.dcm.com/en/team</t>
-        </is>
-      </c>
-      <c r="L309" t="inlineStr"/>
+      <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -17193,12 +15647,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K310" s="2" t="inlineStr">
-        <is>
-          <t>https://www.vertexventures.com/team</t>
-        </is>
-      </c>
-      <c r="L310" s="2" t="inlineStr"/>
+      <c r="K310" s="2" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -17247,12 +15696,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t>https://sosv.com/team/</t>
-        </is>
-      </c>
-      <c r="L311" t="inlineStr"/>
+      <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -17301,12 +15745,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K312" s="2" t="inlineStr">
-        <is>
-          <t>https://www.plugandplaytechcenter.com/about/</t>
-        </is>
-      </c>
-      <c r="L312" s="2" t="inlineStr"/>
+      <c r="K312" s="2" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -17355,12 +15794,7 @@
           <t>Pre-Seed</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t>https://www.techstars.com/about</t>
-        </is>
-      </c>
-      <c r="L313" t="inlineStr"/>
+      <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -17409,12 +15843,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K314" s="2" t="inlineStr">
-        <is>
-          <t>https://www.alchemistaccelerator.com/team</t>
-        </is>
-      </c>
-      <c r="L314" s="2" t="inlineStr"/>
+      <c r="K314" s="2" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -17463,12 +15892,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr">
-        <is>
-          <t>https://pear.vc/team/</t>
-        </is>
-      </c>
-      <c r="L315" t="inlineStr"/>
+      <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -17517,12 +15941,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K316" s="2" t="inlineStr">
-        <is>
-          <t>https://upfront.com/team</t>
-        </is>
-      </c>
-      <c r="L316" s="2" t="inlineStr"/>
+      <c r="K316" s="2" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -17571,12 +15990,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr">
-        <is>
-          <t>https://marchcp.com/team/</t>
-        </is>
-      </c>
-      <c r="L317" t="inlineStr"/>
+      <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -17625,12 +16039,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K318" s="2" t="inlineStr">
-        <is>
-          <t>https://www.drivecapital.com/team</t>
-        </is>
-      </c>
-      <c r="L318" s="2" t="inlineStr"/>
+      <c r="K318" s="2" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -17679,12 +16088,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr">
-        <is>
-          <t>https://revolution.com/team/</t>
-        </is>
-      </c>
-      <c r="L319" t="inlineStr"/>
+      <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -17733,12 +16137,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K320" s="2" t="inlineStr">
-        <is>
-          <t>https://foundrygroup.com/team/</t>
-        </is>
-      </c>
-      <c r="L320" s="2" t="inlineStr"/>
+      <c r="K320" s="2" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -17787,12 +16186,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr">
-        <is>
-          <t>https://costanoa.vc/team/</t>
-        </is>
-      </c>
-      <c r="L321" t="inlineStr"/>
+      <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -17841,12 +16235,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K322" s="2" t="inlineStr">
-        <is>
-          <t>https://www.crosslinkcapital.com/team</t>
-        </is>
-      </c>
-      <c r="L322" s="2" t="inlineStr"/>
+      <c r="K322" s="2" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -17895,12 +16284,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr">
-        <is>
-          <t>https://www.sierraventures.com/team</t>
-        </is>
-      </c>
-      <c r="L323" t="inlineStr"/>
+      <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -17949,12 +16333,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K324" s="2" t="inlineStr">
-        <is>
-          <t>https://www.trinityventures.com/team</t>
-        </is>
-      </c>
-      <c r="L324" s="2" t="inlineStr"/>
+      <c r="K324" s="2" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -18003,12 +16382,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr">
-        <is>
-          <t>https://www.madrona.com/team/</t>
-        </is>
-      </c>
-      <c r="L325" t="inlineStr"/>
+      <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -18057,12 +16431,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K326" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ignitionpartners.com/team</t>
-        </is>
-      </c>
-      <c r="L326" s="2" t="inlineStr"/>
+      <c r="K326" s="2" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -18111,12 +16480,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr">
-        <is>
-          <t>https://voyagercapital.com/team/</t>
-        </is>
-      </c>
-      <c r="L327" t="inlineStr"/>
+      <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -18165,12 +16529,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K328" s="2" t="inlineStr">
-        <is>
-          <t>https://maveron.com/team/</t>
-        </is>
-      </c>
-      <c r="L328" s="2" t="inlineStr"/>
+      <c r="K328" s="2" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -18219,12 +16578,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr">
-        <is>
-          <t>https://www.flybridge.com/team</t>
-        </is>
-      </c>
-      <c r="L329" t="inlineStr"/>
+      <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -18273,12 +16627,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K330" s="2" t="inlineStr">
-        <is>
-          <t>https://www.polarispartners.com/team/</t>
-        </is>
-      </c>
-      <c r="L330" s="2" t="inlineStr"/>
+      <c r="K330" s="2" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -18327,12 +16676,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr">
-        <is>
-          <t>https://openviewpartners.com/team/</t>
-        </is>
-      </c>
-      <c r="L331" t="inlineStr"/>
+      <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -18381,12 +16725,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K332" s="2" t="inlineStr">
-        <is>
-          <t>https://nextviewventures.com/team/</t>
-        </is>
-      </c>
-      <c r="L332" s="2" t="inlineStr"/>
+      <c r="K332" s="2" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -18435,12 +16774,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr">
-        <is>
-          <t>https://underscore.vc/team/</t>
-        </is>
-      </c>
-      <c r="L333" t="inlineStr"/>
+      <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -18489,12 +16823,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K334" s="2" t="inlineStr">
-        <is>
-          <t>https://pillar.vc/team/</t>
-        </is>
-      </c>
-      <c r="L334" s="2" t="inlineStr"/>
+      <c r="K334" s="2" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -18543,12 +16872,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr">
-        <is>
-          <t>https://glasswing.vc/team/</t>
-        </is>
-      </c>
-      <c r="L335" t="inlineStr"/>
+      <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -18597,12 +16921,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K336" s="2" t="inlineStr">
-        <is>
-          <t>https://twosigmaventures.com/team/</t>
-        </is>
-      </c>
-      <c r="L336" s="2" t="inlineStr"/>
+      <c r="K336" s="2" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -18651,12 +16970,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr">
-        <is>
-          <t>https://www.bloombergbeta.com/</t>
-        </is>
-      </c>
-      <c r="L337" t="inlineStr"/>
+      <c r="K337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -18705,12 +17019,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K338" s="2" t="inlineStr">
-        <is>
-          <t>https://comcastventures.com/team/</t>
-        </is>
-      </c>
-      <c r="L338" s="2" t="inlineStr"/>
+      <c r="K338" s="2" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -18759,12 +17068,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr">
-        <is>
-          <t>https://www.citi.com/ventures/team.html</t>
-        </is>
-      </c>
-      <c r="L339" t="inlineStr"/>
+      <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -18813,12 +17117,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K340" s="2" t="inlineStr">
-        <is>
-          <t>https://www.capitaloneventures.com/team</t>
-        </is>
-      </c>
-      <c r="L340" s="2" t="inlineStr"/>
+      <c r="K340" s="2" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -18867,12 +17166,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr">
-        <is>
-          <t>https://www.wellsfargo.com/</t>
-        </is>
-      </c>
-      <c r="L341" t="inlineStr"/>
+      <c r="K341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -18921,12 +17215,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K342" s="2" t="inlineStr">
-        <is>
-          <t>https://www.jpmorgan.com/</t>
-        </is>
-      </c>
-      <c r="L342" s="2" t="inlineStr"/>
+      <c r="K342" s="2" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -18975,12 +17264,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t>https://www.goldmansachs.com/</t>
-        </is>
-      </c>
-      <c r="L343" t="inlineStr"/>
+      <c r="K343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -19029,12 +17313,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K344" s="2" t="inlineStr">
-        <is>
-          <t>https://www.morganstanley.com/</t>
-        </is>
-      </c>
-      <c r="L344" s="2" t="inlineStr"/>
+      <c r="K344" s="2" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -19083,12 +17362,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr">
-        <is>
-          <t>https://www.baincapitalventures.com/team/</t>
-        </is>
-      </c>
-      <c r="L345" t="inlineStr"/>
+      <c r="K345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -19137,12 +17411,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K346" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kkr.com/team</t>
-        </is>
-      </c>
-      <c r="L346" s="2" t="inlineStr"/>
+      <c r="K346" s="2" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -19191,12 +17460,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr">
-        <is>
-          <t>https://www.blackstone.com/our-people/</t>
-        </is>
-      </c>
-      <c r="L347" t="inlineStr"/>
+      <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -19245,12 +17509,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K348" s="2" t="inlineStr">
-        <is>
-          <t>https://www.apollo.com/our-team</t>
-        </is>
-      </c>
-      <c r="L348" s="2" t="inlineStr"/>
+      <c r="K348" s="2" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -19299,12 +17558,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr">
-        <is>
-          <t>https://www.oaktreecapital.com/people</t>
-        </is>
-      </c>
-      <c r="L349" t="inlineStr"/>
+      <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -19353,12 +17607,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K350" s="2" t="inlineStr">
-        <is>
-          <t>https://1984.vc/team</t>
-        </is>
-      </c>
-      <c r="L350" s="2" t="inlineStr"/>
+      <c r="K350" s="2" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -19407,12 +17656,7 @@
           <t>Pre-Seed</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr">
-        <is>
-          <t>https://www.2048.vc/team</t>
-        </is>
-      </c>
-      <c r="L351" t="inlineStr"/>
+      <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -19461,12 +17705,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K352" s="2" t="inlineStr">
-        <is>
-          <t>https://www.abstractvc.com/team</t>
-        </is>
-      </c>
-      <c r="L352" s="2" t="inlineStr"/>
+      <c r="K352" s="2" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -19515,12 +17754,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr">
-        <is>
-          <t>https://acme.vc/team/</t>
-        </is>
-      </c>
-      <c r="L353" t="inlineStr"/>
+      <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -19569,12 +17803,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K354" s="2" t="inlineStr">
-        <is>
-          <t>https://www.actoneventures.com/team</t>
-        </is>
-      </c>
-      <c r="L354" s="2" t="inlineStr"/>
+      <c r="K354" s="2" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -19623,12 +17852,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr">
-        <is>
-          <t>https://www.bcapgroup.com/team</t>
-        </is>
-      </c>
-      <c r="L355" t="inlineStr"/>
+      <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -19677,12 +17901,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K356" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tigerglobal.com/</t>
-        </is>
-      </c>
-      <c r="L356" s="2" t="inlineStr"/>
+      <c r="K356" s="2" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -19731,12 +17950,7 @@
           <t>Series B-Z</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t>https://visionfund.com/team</t>
-        </is>
-      </c>
-      <c r="L357" t="inlineStr"/>
+      <c r="K357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -19785,12 +17999,7 @@
           <t>Series C-Z</t>
         </is>
       </c>
-      <c r="K358" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mubadala.com/en/who-we-are/leadership</t>
-        </is>
-      </c>
-      <c r="L358" s="2" t="inlineStr"/>
+      <c r="K358" s="2" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -19839,12 +18048,7 @@
           <t>Series C-Z</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr">
-        <is>
-          <t>https://www.adia.ae/en/about-adia/board-of-directors</t>
-        </is>
-      </c>
-      <c r="L359" t="inlineStr"/>
+      <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -19893,12 +18097,7 @@
           <t>Series C-Z</t>
         </is>
       </c>
-      <c r="K360" s="2" t="inlineStr">
-        <is>
-          <t>https://www.qia.qa/en/AboutUs/Pages/BoardofDirectors.aspx</t>
-        </is>
-      </c>
-      <c r="L360" s="2" t="inlineStr"/>
+      <c r="K360" s="2" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -19947,12 +18146,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr">
-        <is>
-          <t>https://cathayinnovation.com/team/</t>
-        </is>
-      </c>
-      <c r="L361" t="inlineStr"/>
+      <c r="K361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -20001,12 +18195,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K362" s="2" t="inlineStr">
-        <is>
-          <t>https://www.balderton.com/team/</t>
-        </is>
-      </c>
-      <c r="L362" s="2" t="inlineStr"/>
+      <c r="K362" s="2" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -20055,12 +18244,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr">
-        <is>
-          <t>https://localglobe.vc/team/</t>
-        </is>
-      </c>
-      <c r="L363" t="inlineStr"/>
+      <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -20109,12 +18293,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K364" s="2" t="inlineStr">
-        <is>
-          <t>https://indexventures.com/team/</t>
-        </is>
-      </c>
-      <c r="L364" s="2" t="inlineStr"/>
+      <c r="K364" s="2" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -20163,12 +18342,7 @@
           <t>Pre-Seed</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.afore.vc/team)</t>
-        </is>
-      </c>
-      <c r="L365" t="inlineStr"/>
+      <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -20217,12 +18391,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K366" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.amplifypartners.com/team)</t>
-        </is>
-      </c>
-      <c r="L366" s="2" t="inlineStr"/>
+      <c r="K366" s="2" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -20271,12 +18440,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.array.vc/team)</t>
-        </is>
-      </c>
-      <c r="L367" t="inlineStr"/>
+      <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -20325,12 +18489,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K368" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.artisanalventures.com/team)</t>
-        </is>
-      </c>
-      <c r="L368" s="2" t="inlineStr"/>
+      <c r="K368" s="2" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -20379,12 +18538,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://aspectventures.com/team)</t>
-        </is>
-      </c>
-      <c r="L369" t="inlineStr"/>
+      <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -20433,12 +18587,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K370" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://aviationventures.com/team)</t>
-        </is>
-      </c>
-      <c r="L370" s="2" t="inlineStr"/>
+      <c r="K370" s="2" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -20487,12 +18636,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://base10.vc/team)</t>
-        </is>
-      </c>
-      <c r="L371" t="inlineStr"/>
+      <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -20541,12 +18685,7 @@
           <t>Pre-Seed</t>
         </is>
       </c>
-      <c r="K372" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://betaangels.com/team)</t>
-        </is>
-      </c>
-      <c r="L372" s="2" t="inlineStr"/>
+      <c r="K372" s="2" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -20595,12 +18734,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.blenheimchalcot.com/people)</t>
-        </is>
-      </c>
-      <c r="L373" t="inlineStr"/>
+      <c r="K373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -20649,12 +18783,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K374" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://boldcapitalpartners.com/team)</t>
-        </is>
-      </c>
-      <c r="L374" s="2" t="inlineStr"/>
+      <c r="K374" s="2" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -20703,12 +18832,7 @@
           <t>Pre-Seed</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://bolt.io/team)</t>
-        </is>
-      </c>
-      <c r="L375" t="inlineStr"/>
+      <c r="K375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -20757,12 +18881,7 @@
           <t>Pre-Seed</t>
         </is>
       </c>
-      <c r="K376" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.boost.vc/team)</t>
-        </is>
-      </c>
-      <c r="L376" s="2" t="inlineStr"/>
+      <c r="K376" s="2" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -20811,12 +18930,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://corevc.com/team)</t>
-        </is>
-      </c>
-      <c r="L377" t="inlineStr"/>
+      <c r="K377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -20865,12 +18979,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K378" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.dcvc.com/team)</t>
-        </is>
-      </c>
-      <c r="L378" s="2" t="inlineStr"/>
+      <c r="K378" s="2" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -20919,12 +19028,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.alumniventures.com/team)</t>
-        </is>
-      </c>
-      <c r="L379" t="inlineStr"/>
+      <c r="K379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -20973,12 +19077,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K380" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://a16zcrypto.com/team/)</t>
-        </is>
-      </c>
-      <c r="L380" s="2" t="inlineStr"/>
+      <c r="K380" s="2" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -21027,12 +19126,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://10x.group)</t>
-        </is>
-      </c>
-      <c r="L381" t="inlineStr"/>
+      <c r="K381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -21081,12 +19175,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K382" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://14w.com)</t>
-        </is>
-      </c>
-      <c r="L382" s="2" t="inlineStr"/>
+      <c r="K382" s="2" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -21135,12 +19224,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.thetwentyminutevc.com/about/)</t>
-        </is>
-      </c>
-      <c r="L383" t="inlineStr"/>
+      <c r="K383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -21189,12 +19273,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K384" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.360cap.vc/team)</t>
-        </is>
-      </c>
-      <c r="L384" s="2" t="inlineStr"/>
+      <c r="K384" s="2" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -21243,12 +19322,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.468cap.com/team)</t>
-        </is>
-      </c>
-      <c r="L385" t="inlineStr"/>
+      <c r="K385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -21297,12 +19371,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K386" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://7wireventures.com/team)</t>
-        </is>
-      </c>
-      <c r="L386" s="2" t="inlineStr"/>
+      <c r="K386" s="2" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -21351,12 +19420,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.83north.com/team)</t>
-        </is>
-      </c>
-      <c r="L387" t="inlineStr"/>
+      <c r="K387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -21405,12 +19469,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K388" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://9yardscapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L388" s="2" t="inlineStr"/>
+      <c r="K388" s="2" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -21459,12 +19518,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.acapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L389" t="inlineStr"/>
+      <c r="K389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -21513,12 +19567,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K390" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://abris-capital.com/team)</t>
-        </is>
-      </c>
-      <c r="L390" s="2" t="inlineStr"/>
+      <c r="K390" s="2" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -21567,12 +19616,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.accel.com/team)</t>
-        </is>
-      </c>
-      <c r="L391" t="inlineStr"/>
+      <c r="K391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -21621,12 +19665,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K392" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://active.partners/team)</t>
-        </is>
-      </c>
-      <c r="L392" s="2" t="inlineStr"/>
+      <c r="K392" s="2" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -21675,12 +19714,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://aglaeventures.com)</t>
-        </is>
-      </c>
-      <c r="L393" t="inlineStr"/>
+      <c r="K393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -21729,12 +19763,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K394" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://albacorecapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L394" s="2" t="inlineStr"/>
+      <c r="K394" s="2" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -21783,12 +19812,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://albion.vc/team)</t>
-        </is>
-      </c>
-      <c r="L395" t="inlineStr"/>
+      <c r="K395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -21837,12 +19861,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K396" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://alder.se/team)</t>
-        </is>
-      </c>
-      <c r="L396" s="2" t="inlineStr"/>
+      <c r="K396" s="2" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -21891,12 +19910,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.amadeuscapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L397" t="inlineStr"/>
+      <c r="K397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -21945,12 +19959,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K398" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.aminocapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L398" s="2" t="inlineStr"/>
+      <c r="K398" s="2" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -21999,12 +20008,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.anterracapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L399" t="inlineStr"/>
+      <c r="K399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -22053,12 +20057,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K400" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://apex.ventures/team)</t>
-        </is>
-      </c>
-      <c r="L400" s="2" t="inlineStr"/>
+      <c r="K400" s="2" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -22107,12 +20106,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.aquiline.com/team)</t>
-        </is>
-      </c>
-      <c r="L401" t="inlineStr"/>
+      <c r="K401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -22161,12 +20155,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K402" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://argonauticventures.com/team)</t>
-        </is>
-      </c>
-      <c r="L402" s="2" t="inlineStr"/>
+      <c r="K402" s="2" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -22215,12 +20204,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.ascension.vc/team)</t>
-        </is>
-      </c>
-      <c r="L403" t="inlineStr"/>
+      <c r="K403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -22269,12 +20253,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K404" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.aster.com/team)</t>
-        </is>
-      </c>
-      <c r="L404" s="2" t="inlineStr"/>
+      <c r="K404" s="2" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -22323,12 +20302,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.atlanticlabs.de/team)</t>
-        </is>
-      </c>
-      <c r="L405" t="inlineStr"/>
+      <c r="K405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -22377,12 +20351,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K406" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://atmos.vc/team)</t>
-        </is>
-      </c>
-      <c r="L406" s="2" t="inlineStr"/>
+      <c r="K406" s="2" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -22431,12 +20400,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://autotechvc.com/team)</t>
-        </is>
-      </c>
-      <c r="L407" t="inlineStr"/>
+      <c r="K407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -22485,12 +20449,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K408" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.bcapgroup.com/team)</t>
-        </is>
-      </c>
-      <c r="L408" s="2" t="inlineStr"/>
+      <c r="K408" s="2" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -22539,12 +20498,7 @@
           <t>Pre-Seed</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://backstagecapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L409" t="inlineStr"/>
+      <c r="K409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -22593,12 +20547,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K410" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.bairdcapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L410" s="2" t="inlineStr"/>
+      <c r="K410" s="2" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -22647,12 +20596,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.baloise.com)</t>
-        </is>
-      </c>
-      <c r="L411" t="inlineStr"/>
+      <c r="K411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -22701,12 +20645,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K412" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://bamelevate.com/team)</t>
-        </is>
-      </c>
-      <c r="L412" s="2" t="inlineStr"/>
+      <c r="K412" s="2" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -22755,12 +20694,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://basepartners.com/team)</t>
-        </is>
-      </c>
-      <c r="L413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -22809,12 +20743,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K414" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.bayer.com)</t>
-        </is>
-      </c>
-      <c r="L414" s="2" t="inlineStr"/>
+      <c r="K414" s="2" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -22863,12 +20792,7 @@
           <t>Pre-Seed</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.beepartners.vc/team)</t>
-        </is>
-      </c>
-      <c r="L415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -22917,12 +20841,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K416" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.beringea.com/team)</t>
-        </is>
-      </c>
-      <c r="L416" s="2" t="inlineStr"/>
+      <c r="K416" s="2" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -22971,12 +20890,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://bestport.co.uk/team)</t>
-        </is>
-      </c>
-      <c r="L417" t="inlineStr"/>
+      <c r="K417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -23025,12 +20939,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K418" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.bgf.co.uk/team)</t>
-        </is>
-      </c>
-      <c r="L418" s="2" t="inlineStr"/>
+      <c r="K418" s="2" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -23079,12 +20988,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://bigissueinvest.com/team)</t>
-        </is>
-      </c>
-      <c r="L419" t="inlineStr"/>
+      <c r="K419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -23133,12 +21037,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K420" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://biogenerationventures.com/team)</t>
-        </is>
-      </c>
-      <c r="L420" s="2" t="inlineStr"/>
+      <c r="K420" s="2" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -23187,12 +21086,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.bitkraft.vc/team)</t>
-        </is>
-      </c>
-      <c r="L421" t="inlineStr"/>
+      <c r="K421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -23241,12 +21135,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K422" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://blackbird.vc/team)</t>
-        </is>
-      </c>
-      <c r="L422" s="2" t="inlineStr"/>
+      <c r="K422" s="2" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -23295,12 +21184,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.bonfirevc.com/team)</t>
-        </is>
-      </c>
-      <c r="L423" t="inlineStr"/>
+      <c r="K423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -23349,12 +21233,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K424" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://bregalmilestone.com/team)</t>
-        </is>
-      </c>
-      <c r="L424" s="2" t="inlineStr"/>
+      <c r="K424" s="2" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -23403,12 +21282,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://breega.com/team)</t>
-        </is>
-      </c>
-      <c r="L425" t="inlineStr"/>
+      <c r="K425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -23457,12 +21331,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K426" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.bridgesfundmanagement.com/team)</t>
-        </is>
-      </c>
-      <c r="L426" s="2" t="inlineStr"/>
+      <c r="K426" s="2" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -23511,12 +21380,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://brpx.com/team)</t>
-        </is>
-      </c>
-      <c r="L427" t="inlineStr"/>
+      <c r="K427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -23565,12 +21429,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K428" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.brighteyevc.com/team)</t>
-        </is>
-      </c>
-      <c r="L428" s="2" t="inlineStr"/>
+      <c r="K428" s="2" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -23619,12 +21478,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.britishpatientcapital.co.uk)</t>
-        </is>
-      </c>
-      <c r="L429" t="inlineStr"/>
+      <c r="K429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -23673,12 +21527,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K430" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.brookfield.com/our-team)</t>
-        </is>
-      </c>
-      <c r="L430" s="2" t="inlineStr"/>
+      <c r="K430" s="2" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -23727,12 +21576,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://builders.vc/team)</t>
-        </is>
-      </c>
-      <c r="L431" t="inlineStr"/>
+      <c r="K431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -23781,12 +21625,7 @@
           <t>Series A</t>
         </is>
       </c>
-      <c r="K432" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://calibratevc.com/team)</t>
-        </is>
-      </c>
-      <c r="L432" s="2" t="inlineStr"/>
+      <c r="K432" s="2" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -23835,12 +21674,7 @@
           <t>Pre-Seed</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://calmstorm.vc/team)</t>
-        </is>
-      </c>
-      <c r="L433" t="inlineStr"/>
+      <c r="K433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -23889,12 +21723,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K434" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://cambercreek.com/team)</t>
-        </is>
-      </c>
-      <c r="L434" s="2" t="inlineStr"/>
+      <c r="K434" s="2" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -23943,12 +21772,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://caphorn.vc/team)</t>
-        </is>
-      </c>
-      <c r="L435" t="inlineStr"/>
+      <c r="K435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -23997,12 +21821,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K436" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.catonetworks.com)</t>
-        </is>
-      </c>
-      <c r="L436" s="2" t="inlineStr"/>
+      <c r="K436" s="2" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -24051,12 +21870,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://cavalry.vc/team)</t>
-        </is>
-      </c>
-      <c r="L437" t="inlineStr"/>
+      <c r="K437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -24105,12 +21919,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K438" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://ceic.com/team)</t>
-        </is>
-      </c>
-      <c r="L438" s="2" t="inlineStr"/>
+      <c r="K438" s="2" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -24159,12 +21968,7 @@
           <t>Grant</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://celo.org)</t>
-        </is>
-      </c>
-      <c r="L439" t="inlineStr"/>
+      <c r="K439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -24213,12 +22017,7 @@
           <t>Grant</t>
         </is>
       </c>
-      <c r="K440" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://chain.link)</t>
-        </is>
-      </c>
-      <c r="L440" s="2" t="inlineStr"/>
+      <c r="K440" s="2" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -24267,12 +22066,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://chrysalix.com/team)</t>
-        </is>
-      </c>
-      <c r="L441" t="inlineStr"/>
+      <c r="K441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -24321,12 +22115,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K442" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://www.cinven.com/team)</t>
-        </is>
-      </c>
-      <c r="L442" s="2" t="inlineStr"/>
+      <c r="K442" s="2" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -24375,12 +22164,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://circularitycapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L443" t="inlineStr"/>
+      <c r="K443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -24429,12 +22213,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K444" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://cityblockcapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L444" s="2" t="inlineStr"/>
+      <c r="K444" s="2" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -24483,12 +22262,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://claret-capital.com/team)</t>
-        </is>
-      </c>
-      <c r="L445" t="inlineStr"/>
+      <c r="K445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -24537,12 +22311,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K446" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://clearlake.com/team)</t>
-        </is>
-      </c>
-      <c r="L446" s="2" t="inlineStr"/>
+      <c r="K446" s="2" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -24591,12 +22360,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://clear-sky.com/team)</t>
-        </is>
-      </c>
-      <c r="L447" t="inlineStr"/>
+      <c r="K447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -24645,12 +22409,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K448" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://cmt.digital/team)</t>
-        </is>
-      </c>
-      <c r="L448" s="2" t="inlineStr"/>
+      <c r="K448" s="2" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -24699,12 +22458,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://cobaltcapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L449" t="inlineStr"/>
+      <c r="K449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -24753,12 +22507,7 @@
           <t>Series A</t>
         </is>
       </c>
-      <c r="K450" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://cogitocapital.vc/team)</t>
-        </is>
-      </c>
-      <c r="L450" s="2" t="inlineStr"/>
+      <c r="K450" s="2" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -24807,12 +22556,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://cognitive.vc/team)</t>
-        </is>
-      </c>
-      <c r="L451" t="inlineStr"/>
+      <c r="K451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -24861,12 +22605,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K452" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://cohortcapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L452" s="2" t="inlineStr"/>
+      <c r="K452" s="2" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -24915,12 +22654,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://ventures.coinbase.com/team)</t>
-        </is>
-      </c>
-      <c r="L453" t="inlineStr"/>
+      <c r="K453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
@@ -24969,12 +22703,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K454" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://collabfund.com/team)</t>
-        </is>
-      </c>
-      <c r="L454" s="2" t="inlineStr"/>
+      <c r="K454" s="2" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -25023,12 +22752,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://columbusvp.com/team)</t>
-        </is>
-      </c>
-      <c r="L455" t="inlineStr"/>
+      <c r="K455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -25077,12 +22801,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K456" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://cometlabs.io/team)</t>
-        </is>
-      </c>
-      <c r="L456" s="2" t="inlineStr"/>
+      <c r="K456" s="2" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -25131,12 +22850,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://commerce.vc/team)</t>
-        </is>
-      </c>
-      <c r="L457" t="inlineStr"/>
+      <c r="K457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -25185,12 +22899,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K458" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://concentric.vc/team)</t>
-        </is>
-      </c>
-      <c r="L458" s="2" t="inlineStr"/>
+      <c r="K458" s="2" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -25239,12 +22948,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://concordhp.com/team)</t>
-        </is>
-      </c>
-      <c r="L459" t="inlineStr"/>
+      <c r="K459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -25293,12 +22997,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K460" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://connectventures.co/team)</t>
-        </is>
-      </c>
-      <c r="L460" s="2" t="inlineStr"/>
+      <c r="K460" s="2" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -25347,12 +23046,7 @@
           <t>Pre-Seed</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://conscience.vc/team)</t>
-        </is>
-      </c>
-      <c r="L461" t="inlineStr"/>
+      <c r="K461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
@@ -25401,12 +23095,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K462" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://constructcap.com/team)</t>
-        </is>
-      </c>
-      <c r="L462" s="2" t="inlineStr"/>
+      <c r="K462" s="2" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -25455,12 +23144,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://contourventures.com/team)</t>
-        </is>
-      </c>
-      <c r="L463" t="inlineStr"/>
+      <c r="K463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
@@ -25509,12 +23193,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K464" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://copernion.com/team)</t>
-        </is>
-      </c>
-      <c r="L464" s="2" t="inlineStr"/>
+      <c r="K464" s="2" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -25563,12 +23242,7 @@
           <t>Pre-Seed</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://coplex.com/team)</t>
-        </is>
-      </c>
-      <c r="L465" t="inlineStr"/>
+      <c r="K465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -25617,12 +23291,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K466" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://coralcap.co/team)</t>
-        </is>
-      </c>
-      <c r="L466" s="2" t="inlineStr"/>
+      <c r="K466" s="2" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -25671,12 +23340,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://corenest.co/team)</t>
-        </is>
-      </c>
-      <c r="L467" t="inlineStr"/>
+      <c r="K467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -25725,12 +23389,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K468" s="2" t="inlineStr">
-        <is>
-          <t>https://a16zcrypto.com/about/</t>
-        </is>
-      </c>
-      <c r="L468" s="2" t="inlineStr"/>
+      <c r="K468" s="2" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -25779,12 +23438,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr">
-        <is>
-          <t>https://panteracapital.com/team/</t>
-        </is>
-      </c>
-      <c r="L469" t="inlineStr"/>
+      <c r="K469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -25833,12 +23487,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K470" s="2" t="inlineStr">
-        <is>
-          <t>https://variant.fund/about/</t>
-        </is>
-      </c>
-      <c r="L470" s="2" t="inlineStr"/>
+      <c r="K470" s="2" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -25887,12 +23536,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr">
-        <is>
-          <t>https://framework.ventures/about-us</t>
-        </is>
-      </c>
-      <c r="L471" t="inlineStr"/>
+      <c r="K471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -25941,12 +23585,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K472" s="2" t="inlineStr">
-        <is>
-          <t>https://multicoin.capital/about/</t>
-        </is>
-      </c>
-      <c r="L472" s="2" t="inlineStr"/>
+      <c r="K472" s="2" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -25995,12 +23634,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr">
-        <is>
-          <t>https://x.com/yzilabs/jobs</t>
-        </is>
-      </c>
-      <c r="L473" t="inlineStr"/>
+      <c r="K473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
@@ -26049,12 +23683,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K474" s="2" t="inlineStr">
-        <is>
-          <t>https://blockchaincapital.com/about-us</t>
-        </is>
-      </c>
-      <c r="L474" s="2" t="inlineStr"/>
+      <c r="K474" s="2" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -26103,12 +23732,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr">
-        <is>
-          <t>https://castleisland.vc/team/</t>
-        </is>
-      </c>
-      <c r="L475" t="inlineStr"/>
+      <c r="K475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
@@ -26157,12 +23781,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K476" s="2" t="inlineStr">
-        <is>
-          <t>https://www.fabric.vc/about</t>
-        </is>
-      </c>
-      <c r="L476" s="2" t="inlineStr"/>
+      <c r="K476" s="2" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -26211,12 +23830,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr">
-        <is>
-          <t>https://meetings.hubspot.com/carter-lundy</t>
-        </is>
-      </c>
-      <c r="L477" t="inlineStr"/>
+      <c r="K477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -26265,12 +23879,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K478" s="2" t="inlineStr">
-        <is>
-          <t>https://clearlake.com/about/</t>
-        </is>
-      </c>
-      <c r="L478" s="2" t="inlineStr"/>
+      <c r="K478" s="2" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -26319,12 +23928,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr">
-        <is>
-          <t>https://hf.com/about/</t>
-        </is>
-      </c>
-      <c r="L479" t="inlineStr"/>
+      <c r="K479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
@@ -26373,12 +23977,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K480" s="2" t="inlineStr">
-        <is>
-          <t>https://permira.com/contact-us</t>
-        </is>
-      </c>
-      <c r="L480" s="2" t="inlineStr"/>
+      <c r="K480" s="2" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -26427,12 +24026,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr">
-        <is>
-          <t>https://www.adventinternational.com/about-us/</t>
-        </is>
-      </c>
-      <c r="L481" t="inlineStr"/>
+      <c r="K481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
@@ -26481,12 +24075,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K482" s="2" t="inlineStr">
-        <is>
-          <t>https://warburgpincus.com/team/</t>
-        </is>
-      </c>
-      <c r="L482" s="2" t="inlineStr"/>
+      <c r="K482" s="2" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -26535,12 +24124,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr">
-        <is>
-          <t>https://maki.vc/people/</t>
-        </is>
-      </c>
-      <c r="L483" t="inlineStr"/>
+      <c r="K483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
@@ -26589,12 +24173,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K484" s="2" t="inlineStr">
-        <is>
-          <t>https://moltenventures.com/people/partnership</t>
-        </is>
-      </c>
-      <c r="L484" s="2" t="inlineStr"/>
+      <c r="K484" s="2" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -26643,12 +24222,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr">
-        <is>
-          <t>https://moltenventures.com/people/partnership</t>
-        </is>
-      </c>
-      <c r="L485" t="inlineStr"/>
+      <c r="K485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
@@ -26697,12 +24271,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K486" s="2" t="inlineStr">
-        <is>
-          <t>https://mmc.vc/about-us/</t>
-        </is>
-      </c>
-      <c r="L486" s="2" t="inlineStr"/>
+      <c r="K486" s="2" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -26751,12 +24320,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr">
-        <is>
-          <t>https://www.amadeuscapital.com/the-team/</t>
-        </is>
-      </c>
-      <c r="L487" t="inlineStr"/>
+      <c r="K487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
@@ -26805,12 +24369,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K488" s="2" t="inlineStr">
-        <is>
-          <t>https://scottish-enterprise.com/contact-us</t>
-        </is>
-      </c>
-      <c r="L488" s="2" t="inlineStr"/>
+      <c r="K488" s="2" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -26859,12 +24418,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr">
-        <is>
-          <t>https://enterprise-ireland.com/en/contact-us</t>
-        </is>
-      </c>
-      <c r="L489" t="inlineStr"/>
+      <c r="K489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
@@ -26913,12 +24467,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K490" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kfw-capital.de/Über-uns/Team/</t>
-        </is>
-      </c>
-      <c r="L490" s="2" t="inlineStr"/>
+      <c r="K490" s="2" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -26967,12 +24516,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr">
-        <is>
-          <t>https://coparion.vc/#tmpl-team</t>
-        </is>
-      </c>
-      <c r="L491" t="inlineStr"/>
+      <c r="K491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -27021,12 +24565,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K492" s="2" t="inlineStr">
-        <is>
-          <t>https://uvcpartners.com/our-team</t>
-        </is>
-      </c>
-      <c r="L492" s="2" t="inlineStr"/>
+      <c r="K492" s="2" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -27075,12 +24614,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr">
-        <is>
-          <t>https://www.project-a.vc/team</t>
-        </is>
-      </c>
-      <c r="L493" t="inlineStr"/>
+      <c r="K493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -27129,12 +24663,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K494" s="2" t="inlineStr">
-        <is>
-          <t>https://globalfounderscapital.com/</t>
-        </is>
-      </c>
-      <c r="L494" s="2" t="inlineStr"/>
+      <c r="K494" s="2" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -27183,12 +24712,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr">
-        <is>
-          <t>https://credoventures.com/meet-us</t>
-        </is>
-      </c>
-      <c r="L495" t="inlineStr"/>
+      <c r="K495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
@@ -27237,12 +24761,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K496" s="2" t="inlineStr">
-        <is>
-          <t>https://www.HugeDomains.com/about.cfm</t>
-        </is>
-      </c>
-      <c r="L496" s="2" t="inlineStr"/>
+      <c r="K496" s="2" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -27291,12 +24810,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr">
-        <is>
-          <t>https://www.smok.vc/team/</t>
-        </is>
-      </c>
-      <c r="L497" t="inlineStr"/>
+      <c r="K497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
@@ -27345,12 +24859,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K498" s="2" t="inlineStr">
-        <is>
-          <t>https://sc-ventures.com/about-us</t>
-        </is>
-      </c>
-      <c r="L498" s="2" t="inlineStr"/>
+      <c r="K498" s="2" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -27399,12 +24908,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr">
-        <is>
-          <t>https://launchub.com/#8dc2a10212b144d8acacf1661a3c67fc</t>
-        </is>
-      </c>
-      <c r="L499" t="inlineStr"/>
+      <c r="K499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
@@ -27453,12 +24957,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K500" s="2" t="inlineStr">
-        <is>
-          <t>https://revo.vc/about/</t>
-        </is>
-      </c>
-      <c r="L500" s="2" t="inlineStr"/>
+      <c r="K500" s="2" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -27507,12 +25006,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr">
-        <is>
-          <t>https://212.vc/team/</t>
-        </is>
-      </c>
-      <c r="L501" t="inlineStr"/>
+      <c r="K501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
@@ -27561,12 +25055,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K502" s="2" t="inlineStr">
-        <is>
-          <t>https://eurazeo.com/fr/contacts</t>
-        </is>
-      </c>
-      <c r="L502" s="2" t="inlineStr"/>
+      <c r="K502" s="2" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -27615,12 +25104,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr">
-        <is>
-          <t>https://eurazeo.com/fr/contacts</t>
-        </is>
-      </c>
-      <c r="L503" t="inlineStr"/>
+      <c r="K503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
@@ -27669,12 +25153,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K504" s="2" t="inlineStr">
-        <is>
-          <t>https://ventures.orange.com/about/</t>
-        </is>
-      </c>
-      <c r="L504" s="2" t="inlineStr"/>
+      <c r="K504" s="2" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -27723,12 +25202,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr">
-        <is>
-          <t>https://daphni.com/about-us</t>
-        </is>
-      </c>
-      <c r="L505" t="inlineStr"/>
+      <c r="K505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
@@ -27777,12 +25251,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K506" s="2" t="inlineStr">
-        <is>
-          <t>https://ventechvc.com/people</t>
-        </is>
-      </c>
-      <c r="L506" s="2" t="inlineStr"/>
+      <c r="K506" s="2" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -27831,12 +25300,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr">
-        <is>
-          <t>https://www.omnescapital.com/about-us</t>
-        </is>
-      </c>
-      <c r="L507" t="inlineStr"/>
+      <c r="K507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
@@ -27885,12 +25349,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K508" s="2" t="inlineStr">
-        <is>
-          <t>https://www.seventure.fr/contact/</t>
-        </is>
-      </c>
-      <c r="L508" s="2" t="inlineStr"/>
+      <c r="K508" s="2" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -27939,12 +25398,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr">
-        <is>
-          <t>https://www.kurmapartners.com/en</t>
-        </is>
-      </c>
-      <c r="L509" t="inlineStr"/>
+      <c r="K509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
@@ -27993,12 +25447,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K510" s="2" t="inlineStr">
-        <is>
-          <t>https://lspvc.com/about/people</t>
-        </is>
-      </c>
-      <c r="L510" s="2" t="inlineStr"/>
+      <c r="K510" s="2" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -28047,12 +25496,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr">
-        <is>
-          <t>https://biogenerationventures.com/en/about_us/</t>
-        </is>
-      </c>
-      <c r="L511" t="inlineStr"/>
+      <c r="K511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
@@ -28101,12 +25545,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K512" s="2" t="inlineStr">
-        <is>
-          <t>https://primeventures.com/people/</t>
-        </is>
-      </c>
-      <c r="L512" s="2" t="inlineStr"/>
+      <c r="K512" s="2" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -28155,12 +25594,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr">
-        <is>
-          <t>https://nordiccapital.com/about-us/</t>
-        </is>
-      </c>
-      <c r="L513" t="inlineStr"/>
+      <c r="K513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
@@ -28209,12 +25643,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K514" s="2" t="inlineStr">
-        <is>
-          <t>https://summaequity.com/company/about-us/</t>
-        </is>
-      </c>
-      <c r="L514" s="2" t="inlineStr"/>
+      <c r="K514" s="2" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -28263,12 +25692,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr">
-        <is>
-          <t>https://altor.com/our-team</t>
-        </is>
-      </c>
-      <c r="L515" t="inlineStr"/>
+      <c r="K515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
@@ -28317,12 +25741,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K516" s="2" t="inlineStr">
-        <is>
-          <t>https://polarisequity.dk#contact</t>
-        </is>
-      </c>
-      <c r="L516" s="2" t="inlineStr"/>
+      <c r="K516" s="2" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -28371,12 +25790,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr">
-        <is>
-          <t>https://kinnevik.com/team/</t>
-        </is>
-      </c>
-      <c r="L517" t="inlineStr"/>
+      <c r="K517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
@@ -28425,12 +25839,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K518" s="2" t="inlineStr">
-        <is>
-          <t>https://vnv.global/about/</t>
-        </is>
-      </c>
-      <c r="L518" s="2" t="inlineStr"/>
+      <c r="K518" s="2" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -28479,12 +25888,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr">
-        <is>
-          <t>https://adevinta.com/brands/</t>
-        </is>
-      </c>
-      <c r="L519" t="inlineStr"/>
+      <c r="K519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
@@ -28533,12 +25937,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K520" s="2" t="inlineStr">
-        <is>
-          <t>https://schibsted.com/about/</t>
-        </is>
-      </c>
-      <c r="L520" s="2" t="inlineStr"/>
+      <c r="K520" s="2" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -28587,12 +25986,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr">
-        <is>
-          <t>https://prosus.com/about-us</t>
-        </is>
-      </c>
-      <c r="L521" t="inlineStr"/>
+      <c r="K521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
@@ -28641,12 +26035,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K522" s="2" t="inlineStr">
-        <is>
-          <t>https://naspers.com/our-impact/our-approach/our-people</t>
-        </is>
-      </c>
-      <c r="L522" s="2" t="inlineStr"/>
+      <c r="K522" s="2" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -28695,12 +26084,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr">
-        <is>
-          <t>https://foundersfactory.com/about-us/</t>
-        </is>
-      </c>
-      <c r="L523" t="inlineStr"/>
+      <c r="K523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
@@ -28749,12 +26133,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K524" s="2" t="inlineStr">
-        <is>
-          <t>https://www.joinef.com/about-us/</t>
-        </is>
-      </c>
-      <c r="L524" s="2" t="inlineStr"/>
+      <c r="K524" s="2" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -28803,12 +26182,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr">
-        <is>
-          <t>https://wayra.com/about-us</t>
-        </is>
-      </c>
-      <c r="L525" t="inlineStr"/>
+      <c r="K525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
@@ -28857,12 +26231,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K526" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ibm.com/case-studies/avid-solutions-international?lnk=hpcs2us</t>
-        </is>
-      </c>
-      <c r="L526" s="2" t="inlineStr"/>
+      <c r="K526" s="2" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -28911,12 +26280,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr">
-        <is>
-          <t>https://toyota.ventures/#about-us</t>
-        </is>
-      </c>
-      <c r="L527" t="inlineStr"/>
+      <c r="K527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
@@ -28965,12 +26329,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K528" s="2" t="inlineStr">
-        <is>
-          <t>https://bmwiventures.com/about-us</t>
-        </is>
-      </c>
-      <c r="L528" s="2" t="inlineStr"/>
+      <c r="K528" s="2" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -29019,12 +26378,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr">
-        <is>
-          <t>https://www.maersk.com/transportation-services/ground-freight?utm_campaign=NAM_MCO_BRO_EN_MM_FBM_HERO-BANNER-MGF-Q225_Q2_2025_127200&amp;utm_source=salescollateral&amp;utm_medium=na&amp;utm_content=Hero-Banner-MGF-Q2-2025</t>
-        </is>
-      </c>
-      <c r="L529" t="inlineStr"/>
+      <c r="K529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
@@ -29073,12 +26427,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K530" s="2" t="inlineStr">
-        <is>
-          <t>https://equinor.com/about-us</t>
-        </is>
-      </c>
-      <c r="L530" s="2" t="inlineStr"/>
+      <c r="K530" s="2" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -29127,12 +26476,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr">
-        <is>
-          <t>https://rbvc.com/team/</t>
-        </is>
-      </c>
-      <c r="L531" t="inlineStr"/>
+      <c r="K531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
@@ -29181,12 +26525,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K532" s="2" t="inlineStr">
-        <is>
-          <t>https://tdk-ventures.com/team/</t>
-        </is>
-      </c>
-      <c r="L532" s="2" t="inlineStr"/>
+      <c r="K532" s="2" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -29235,12 +26574,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr">
-        <is>
-          <t>https://blogs.nvidia.com/blog/ai-agents-intelligent-document-processing</t>
-        </is>
-      </c>
-      <c r="L533" t="inlineStr"/>
+      <c r="K533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
@@ -29289,12 +26623,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K534" s="2" t="inlineStr">
-        <is>
-          <t>https://amd.com/en/products/processors/consumer/agent-computers.html</t>
-        </is>
-      </c>
-      <c r="L534" s="2" t="inlineStr"/>
+      <c r="K534" s="2" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -29343,12 +26672,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr">
-        <is>
-          <t>https://strive.vc/about_us</t>
-        </is>
-      </c>
-      <c r="L535" t="inlineStr"/>
+      <c r="K535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
@@ -29397,12 +26721,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K536" s="2" t="inlineStr">
-        <is>
-          <t>https://www.chiratae.com/about-us/</t>
-        </is>
-      </c>
-      <c r="L536" s="2" t="inlineStr"/>
+      <c r="K536" s="2" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -29451,12 +26770,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr">
-        <is>
-          <t>https://nexusvp.com/about/</t>
-        </is>
-      </c>
-      <c r="L537" t="inlineStr"/>
+      <c r="K537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
@@ -29505,12 +26819,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K538" s="2" t="inlineStr">
-        <is>
-          <t>https://a91partners.com/about-us</t>
-        </is>
-      </c>
-      <c r="L538" s="2" t="inlineStr"/>
+      <c r="K538" s="2" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -29559,12 +26868,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr">
-        <is>
-          <t>https://waterbridge.vc/about-us/</t>
-        </is>
-      </c>
-      <c r="L539" t="inlineStr"/>
+      <c r="K539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
@@ -29613,12 +26917,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K540" s="2" t="inlineStr">
-        <is>
-          <t>https://primevp.in/about-us</t>
-        </is>
-      </c>
-      <c r="L540" s="2" t="inlineStr"/>
+      <c r="K540" s="2" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -29667,12 +26966,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr">
-        <is>
-          <t>https://ivycapventures.com/about-us</t>
-        </is>
-      </c>
-      <c r="L541" t="inlineStr"/>
+      <c r="K541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
@@ -29721,12 +27015,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K542" s="2" t="inlineStr">
-        <is>
-          <t>https://www.inflexor.vc/about-us#Philosophy</t>
-        </is>
-      </c>
-      <c r="L542" s="2" t="inlineStr"/>
+      <c r="K542" s="2" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -29775,12 +27064,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr">
-        <is>
-          <t>https://alteriacapital.com/team/</t>
-        </is>
-      </c>
-      <c r="L543" t="inlineStr"/>
+      <c r="K543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
@@ -29829,12 +27113,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K544" s="2" t="inlineStr">
-        <is>
-          <t>https://trifectacapital.in/people/</t>
-        </is>
-      </c>
-      <c r="L544" s="2" t="inlineStr"/>
+      <c r="K544" s="2" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -29883,12 +27162,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr">
-        <is>
-          <t>https://aavishkaarcapital.in/about/</t>
-        </is>
-      </c>
-      <c r="L545" t="inlineStr"/>
+      <c r="K545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
@@ -29937,12 +27211,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K546" s="2" t="inlineStr">
-        <is>
-          <t>https://elevarequity.com/about/</t>
-        </is>
-      </c>
-      <c r="L546" s="2" t="inlineStr"/>
+      <c r="K546" s="2" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -29991,12 +27260,7 @@
           <t>Series A</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://blossomcap.com/team)</t>
-        </is>
-      </c>
-      <c r="L547" t="inlineStr"/>
+      <c r="K547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" s="2" t="inlineStr">
@@ -30045,12 +27309,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K548" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://felixcap.com/team)</t>
-        </is>
-      </c>
-      <c r="L548" s="2" t="inlineStr"/>
+      <c r="K548" s="2" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -30099,12 +27358,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://moltenventures.com/team)</t>
-        </is>
-      </c>
-      <c r="L549" t="inlineStr"/>
+      <c r="K549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
@@ -30153,12 +27407,7 @@
           <t>Series B-Z</t>
         </is>
       </c>
-      <c r="K550" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://motivepartners.com/team)</t>
-        </is>
-      </c>
-      <c r="L550" s="2" t="inlineStr"/>
+      <c r="K550" s="2" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -30207,12 +27456,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://qimingvc.com/team)</t>
-        </is>
-      </c>
-      <c r="L551" t="inlineStr"/>
+      <c r="K551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">
@@ -30261,12 +27505,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K552" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://gsrventuresglobal.com/team)</t>
-        </is>
-      </c>
-      <c r="L552" s="2" t="inlineStr"/>
+      <c r="K552" s="2" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -30315,12 +27554,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr">
-        <is>
-          <t>[Team/Contact](http://zhenfund.com/team)</t>
-        </is>
-      </c>
-      <c r="L553" t="inlineStr"/>
+      <c r="K553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
@@ -30369,12 +27603,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K554" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://plumalley.co/team)</t>
-        </is>
-      </c>
-      <c r="L554" s="2" t="inlineStr"/>
+      <c r="K554" s="2" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -30423,12 +27652,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://initialized.com/team)</t>
-        </is>
-      </c>
-      <c r="L555" t="inlineStr"/>
+      <c r="K555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
@@ -30477,12 +27701,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K556" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://foundamental.com/team)</t>
-        </is>
-      </c>
-      <c r="L556" s="2" t="inlineStr"/>
+      <c r="K556" s="2" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -30531,12 +27750,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://playfaircapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L557" t="inlineStr"/>
+      <c r="K557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
@@ -30585,12 +27799,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K558" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://beringea.com/team)</t>
-        </is>
-      </c>
-      <c r="L558" s="2" t="inlineStr"/>
+      <c r="K558" s="2" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -30639,12 +27848,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://airstreet.com/team)</t>
-        </is>
-      </c>
-      <c r="L559" t="inlineStr"/>
+      <c r="K559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
@@ -30693,12 +27897,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K560" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://outwardvc.com/team)</t>
-        </is>
-      </c>
-      <c r="L560" s="2" t="inlineStr"/>
+      <c r="K560" s="2" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -30747,12 +27946,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://episode1.com/team)</t>
-        </is>
-      </c>
-      <c r="L561" t="inlineStr"/>
+      <c r="K561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
@@ -30801,12 +27995,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K562" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://kindredcapital.vc/team)</t>
-        </is>
-      </c>
-      <c r="L562" s="2" t="inlineStr"/>
+      <c r="K562" s="2" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -30855,12 +28044,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://project-a.com/team)</t>
-        </is>
-      </c>
-      <c r="L563" t="inlineStr"/>
+      <c r="K563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
@@ -30909,12 +28093,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K564" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://picuscap.com/team)</t>
-        </is>
-      </c>
-      <c r="L564" s="2" t="inlineStr"/>
+      <c r="K564" s="2" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -30963,12 +28142,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://fly.vc/team)</t>
-        </is>
-      </c>
-      <c r="L565" t="inlineStr"/>
+      <c r="K565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
@@ -31017,12 +28191,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K566" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://korelyacapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L566" s="2" t="inlineStr"/>
+      <c r="K566" s="2" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -31071,12 +28240,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://eurazeo.com/team)</t>
-        </is>
-      </c>
-      <c r="L567" t="inlineStr"/>
+      <c r="K567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
@@ -31125,12 +28289,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K568" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://ventechvc.com/team)</t>
-        </is>
-      </c>
-      <c r="L568" s="2" t="inlineStr"/>
+      <c r="K568" s="2" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -31179,12 +28338,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://breega.com/team)</t>
-        </is>
-      </c>
-      <c r="L569" t="inlineStr"/>
+      <c r="K569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" s="2" t="inlineStr">
@@ -31233,12 +28387,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K570" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://aglaeventures.com/team)</t>
-        </is>
-      </c>
-      <c r="L570" s="2" t="inlineStr"/>
+      <c r="K570" s="2" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -31287,12 +28436,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://heartcore.com/team)</t>
-        </is>
-      </c>
-      <c r="L571" t="inlineStr"/>
+      <c r="K571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" s="2" t="inlineStr">
@@ -31341,12 +28485,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K572" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://byfounders.vc/team)</t>
-        </is>
-      </c>
-      <c r="L572" s="2" t="inlineStr"/>
+      <c r="K572" s="2" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -31395,12 +28534,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://inventure.vc/team)</t>
-        </is>
-      </c>
-      <c r="L573" t="inlineStr"/>
+      <c r="K573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
@@ -31449,12 +28583,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K574" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://maki.vc/team)</t>
-        </is>
-      </c>
-      <c r="L574" s="2" t="inlineStr"/>
+      <c r="K574" s="2" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -31503,12 +28632,7 @@
           <t>Pre-Seed</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://icebreaker.vc/team)</t>
-        </is>
-      </c>
-      <c r="L575" t="inlineStr"/>
+      <c r="K575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
@@ -31557,12 +28681,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K576" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://speedinvest.com/team)</t>
-        </is>
-      </c>
-      <c r="L576" s="2" t="inlineStr"/>
+      <c r="K576" s="2" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -31611,12 +28730,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://dayonecapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L577" t="inlineStr"/>
+      <c r="K577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
@@ -31665,12 +28779,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K578" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://credoventures.com/team)</t>
-        </is>
-      </c>
-      <c r="L578" s="2" t="inlineStr"/>
+      <c r="K578" s="2" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -31719,12 +28828,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://inovo.vc/team)</t>
-        </is>
-      </c>
-      <c r="L579" t="inlineStr"/>
+      <c r="K579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" s="2" t="inlineStr">
@@ -31773,12 +28877,7 @@
           <t>Series A</t>
         </is>
       </c>
-      <c r="K580" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://otb.vc/team)</t>
-        </is>
-      </c>
-      <c r="L580" s="2" t="inlineStr"/>
+      <c r="K580" s="2" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -31827,12 +28926,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://vnv.global/team)</t>
-        </is>
-      </c>
-      <c r="L581" t="inlineStr"/>
+      <c r="K581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" s="2" t="inlineStr">
@@ -31881,12 +28975,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K582" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://kinnevik.com/team)</t>
-        </is>
-      </c>
-      <c r="L582" s="2" t="inlineStr"/>
+      <c r="K582" s="2" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -31935,12 +29024,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://mangrove.vc/team)</t>
-        </is>
-      </c>
-      <c r="L583" t="inlineStr"/>
+      <c r="K583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
@@ -31989,12 +29073,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K584" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://pauaventures.com/team)</t>
-        </is>
-      </c>
-      <c r="L584" s="2" t="inlineStr"/>
+      <c r="K584" s="2" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -32043,12 +29122,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://cavalry.vc/team)</t>
-        </is>
-      </c>
-      <c r="L585" t="inlineStr"/>
+      <c r="K585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
@@ -32097,12 +29171,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K586" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://capnamic.com/team)</t>
-        </is>
-      </c>
-      <c r="L586" s="2" t="inlineStr"/>
+      <c r="K586" s="2" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -32151,12 +29220,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://senovo.vc/team)</t>
-        </is>
-      </c>
-      <c r="L587" t="inlineStr"/>
+      <c r="K587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
@@ -32205,12 +29269,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K588" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://nautacapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L588" s="2" t="inlineStr"/>
+      <c r="K588" s="2" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -32259,12 +29318,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://kiboventures.com/team)</t>
-        </is>
-      </c>
-      <c r="L589" t="inlineStr"/>
+      <c r="K589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
@@ -32313,12 +29367,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K590" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://jme.vc/team)</t>
-        </is>
-      </c>
-      <c r="L590" s="2" t="inlineStr"/>
+      <c r="K590" s="2" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -32367,12 +29416,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://samaipata.vc/team)</t>
-        </is>
-      </c>
-      <c r="L591" t="inlineStr"/>
+      <c r="K591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
@@ -32421,12 +29465,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K592" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://p101.it/team)</t>
-        </is>
-      </c>
-      <c r="L592" s="2" t="inlineStr"/>
+      <c r="K592" s="2" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -32475,12 +29514,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://unitedventures.com/team)</t>
-        </is>
-      </c>
-      <c r="L593" t="inlineStr"/>
+      <c r="K593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
@@ -32529,12 +29563,7 @@
           <t>Late Stage</t>
         </is>
       </c>
-      <c r="K594" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://carmignac.com/team)</t>
-        </is>
-      </c>
-      <c r="L594" s="2" t="inlineStr"/>
+      <c r="K594" s="2" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -32583,12 +29612,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://mourocapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L595" t="inlineStr"/>
+      <c r="K595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
@@ -32637,12 +29661,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K596" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://breega.com/team)</t>
-        </is>
-      </c>
-      <c r="L596" s="2" t="inlineStr"/>
+      <c r="K596" s="2" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -32691,12 +29710,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://venturefriends.vc/team)</t>
-        </is>
-      </c>
-      <c r="L597" t="inlineStr"/>
+      <c r="K597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
@@ -32745,12 +29759,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K598" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://marathon.vc/team)</t>
-        </is>
-      </c>
-      <c r="L598" s="2" t="inlineStr"/>
+      <c r="K598" s="2" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -32799,12 +29808,7 @@
           <t>Seed</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://bigpi.vc/team)</t>
-        </is>
-      </c>
-      <c r="L599" t="inlineStr"/>
+      <c r="K599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
@@ -32853,12 +29857,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K600" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://endeavor.org/team)</t>
-        </is>
-      </c>
-      <c r="L600" s="2" t="inlineStr"/>
+      <c r="K600" s="2" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -32907,12 +29906,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://quona.com/team)</t>
-        </is>
-      </c>
-      <c r="L601" t="inlineStr"/>
+      <c r="K601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
@@ -32961,12 +29955,7 @@
           <t>Series A</t>
         </is>
       </c>
-      <c r="K602" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://elevarequity.com/team)</t>
-        </is>
-      </c>
-      <c r="L602" s="2" t="inlineStr"/>
+      <c r="K602" s="2" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -33015,12 +30004,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://omnivore.vc/team)</t>
-        </is>
-      </c>
-      <c r="L603" t="inlineStr"/>
+      <c r="K603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
@@ -33069,12 +30053,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K604" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://blume.vc/team)</t>
-        </is>
-      </c>
-      <c r="L604" s="2" t="inlineStr"/>
+      <c r="K604" s="2" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -33123,12 +30102,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://kalaari.com/team)</t>
-        </is>
-      </c>
-      <c r="L605" t="inlineStr"/>
+      <c r="K605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
@@ -33177,12 +30151,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K606" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://chiratae.com/team)</t>
-        </is>
-      </c>
-      <c r="L606" s="2" t="inlineStr"/>
+      <c r="K606" s="2" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -33231,12 +30200,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://nexusvp.com/team)</t>
-        </is>
-      </c>
-      <c r="L607" t="inlineStr"/>
+      <c r="K607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="inlineStr">
@@ -33285,12 +30249,7 @@
           <t>Series B-Z</t>
         </is>
       </c>
-      <c r="K608" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://ironpillarfund.com/team)</t>
-        </is>
-      </c>
-      <c r="L608" s="2" t="inlineStr"/>
+      <c r="K608" s="2" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -33339,12 +30298,7 @@
           <t>Series B-Z</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://a91partners.com/team)</t>
-        </is>
-      </c>
-      <c r="L609" t="inlineStr"/>
+      <c r="K609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
@@ -33393,12 +30347,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K610" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://jungle.vc/team)</t>
-        </is>
-      </c>
-      <c r="L610" s="2" t="inlineStr"/>
+      <c r="K610" s="2" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -33447,12 +30396,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://goldengate.vc/team)</t>
-        </is>
-      </c>
-      <c r="L611" t="inlineStr"/>
+      <c r="K611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" s="2" t="inlineStr">
@@ -33501,12 +30445,7 @@
           <t>Series A</t>
         </is>
       </c>
-      <c r="K612" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://monkshill.com/team)</t>
-        </is>
-      </c>
-      <c r="L612" s="2" t="inlineStr"/>
+      <c r="K612" s="2" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -33555,12 +30494,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://openspace.vc/team)</t>
-        </is>
-      </c>
-      <c r="L613" t="inlineStr"/>
+      <c r="K613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="inlineStr">
@@ -33609,12 +30543,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K614" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://insignia.vc/team)</t>
-        </is>
-      </c>
-      <c r="L614" s="2" t="inlineStr"/>
+      <c r="K614" s="2" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -33663,12 +30592,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://alphajwc.com/team)</t>
-        </is>
-      </c>
-      <c r="L615" t="inlineStr"/>
+      <c r="K615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" s="2" t="inlineStr">
@@ -33717,12 +30641,7 @@
           <t>Pre-Seed / Seed</t>
         </is>
       </c>
-      <c r="K616" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://east.vc/team)</t>
-        </is>
-      </c>
-      <c r="L616" s="2" t="inlineStr"/>
+      <c r="K616" s="2" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -33771,12 +30690,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://acv.vc/team)</t>
-        </is>
-      </c>
-      <c r="L617" t="inlineStr"/>
+      <c r="K617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="inlineStr">
@@ -33825,12 +30739,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K618" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://kejoracapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L618" s="2" t="inlineStr"/>
+      <c r="K618" s="2" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -33879,12 +30788,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://gobi.vc/team)</t>
-        </is>
-      </c>
-      <c r="L619" t="inlineStr"/>
+      <c r="K619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" s="2" t="inlineStr">
@@ -33933,12 +30837,7 @@
           <t>Series A-Z</t>
         </is>
       </c>
-      <c r="K620" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://squarepegcap.com/team)</t>
-        </is>
-      </c>
-      <c r="L620" s="2" t="inlineStr"/>
+      <c r="K620" s="2" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -33987,12 +30886,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://blackbird.vc/team)</t>
-        </is>
-      </c>
-      <c r="L621" t="inlineStr"/>
+      <c r="K621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" s="2" t="inlineStr">
@@ -34041,12 +30935,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K622" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://airtree.vc/team)</t>
-        </is>
-      </c>
-      <c r="L622" s="2" t="inlineStr"/>
+      <c r="K622" s="2" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -34095,12 +30984,7 @@
           <t>Seed / Series A</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://mseq.vc/team)</t>
-        </is>
-      </c>
-      <c r="L623" t="inlineStr"/>
+      <c r="K623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" s="2" t="inlineStr">
@@ -34149,12 +31033,7 @@
           <t>Seed / Series A-Z</t>
         </is>
       </c>
-      <c r="K624" s="2" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://globalfounderscapital.com/team)</t>
-        </is>
-      </c>
-      <c r="L624" s="2" t="inlineStr"/>
+      <c r="K624" s="2" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -34203,12 +31082,7 @@
           <t>Series C-Z</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr">
-        <is>
-          <t>[Team/Contact](https://valorep.com/team)</t>
-        </is>
-      </c>
-      <c r="L625" t="inlineStr"/>
+      <c r="K625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" s="2" t="inlineStr">
@@ -34259,11 +31133,6 @@
       </c>
       <c r="K626" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://sequoiacap.com/our-team/)</t>
-        </is>
-      </c>
-      <c r="L626" s="2" t="inlineStr">
-        <is>
           <t>Top tier VC</t>
         </is>
       </c>
@@ -34317,11 +31186,6 @@
       </c>
       <c r="K627" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://a16z.com/about/team/)</t>
-        </is>
-      </c>
-      <c r="L627" t="inlineStr">
-        <is>
           <t>Major tech focus</t>
         </is>
       </c>
@@ -34375,11 +31239,6 @@
       </c>
       <c r="K628" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://www.iqt.org/about/our-team)</t>
-        </is>
-      </c>
-      <c r="L628" s="2" t="inlineStr">
-        <is>
           <t>US Intelligence community fund</t>
         </is>
       </c>
@@ -34433,11 +31292,6 @@
       </c>
       <c r="K629" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://shieldcap.com/team/)</t>
-        </is>
-      </c>
-      <c r="L629" t="inlineStr">
-        <is>
           <t>Frontier technologies</t>
         </is>
       </c>
@@ -34491,11 +31345,6 @@
       </c>
       <c r="K630" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://foundersfund.com/our_team)</t>
-        </is>
-      </c>
-      <c r="L630" s="2" t="inlineStr">
-        <is>
           <t>Contrarian tech investments</t>
         </is>
       </c>
@@ -34549,11 +31398,6 @@
       </c>
       <c r="K631" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://500.co/team)</t>
-        </is>
-      </c>
-      <c r="L631" t="inlineStr">
-        <is>
           <t>Global footprint</t>
         </is>
       </c>
@@ -34607,11 +31451,6 @@
       </c>
       <c r="K632" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://partechpartners.com/team/)</t>
-        </is>
-      </c>
-      <c r="L632" s="2" t="inlineStr">
-        <is>
           <t>Strong Africa presence</t>
         </is>
       </c>
@@ -34665,11 +31504,6 @@
       </c>
       <c r="K633" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://ycombinator.com/about)</t>
-        </is>
-      </c>
-      <c r="L633" t="inlineStr">
-        <is>
           <t>Top startup accelerator</t>
         </is>
       </c>
@@ -34723,11 +31557,6 @@
       </c>
       <c r="K634" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://accel.com/team)</t>
-        </is>
-      </c>
-      <c r="L634" s="2" t="inlineStr">
-        <is>
           <t>Early and growth stage</t>
         </is>
       </c>
@@ -34781,11 +31610,6 @@
       </c>
       <c r="K635" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://lsvp.com/lightspeed-team/)</t>
-        </is>
-      </c>
-      <c r="L635" t="inlineStr">
-        <is>
           <t>Enterprise focus</t>
         </is>
       </c>
@@ -34839,11 +31663,6 @@
       </c>
       <c r="K636" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://indexventures.com/team/)</t>
-        </is>
-      </c>
-      <c r="L636" s="2" t="inlineStr">
-        <is>
           <t>European and US roots</t>
         </is>
       </c>
@@ -34897,11 +31716,6 @@
       </c>
       <c r="K637" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://bvp.com/team)</t>
-        </is>
-      </c>
-      <c r="L637" t="inlineStr">
-        <is>
           <t>Cloud infrastructure focus</t>
         </is>
       </c>
@@ -34955,11 +31769,6 @@
       </c>
       <c r="K638" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://benchmark.com/)</t>
-        </is>
-      </c>
-      <c r="L638" s="2" t="inlineStr">
-        <is>
           <t>Early stage focus</t>
         </is>
       </c>
@@ -35013,11 +31822,6 @@
       </c>
       <c r="K639" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://generalcatalyst.com/team)</t>
-        </is>
-      </c>
-      <c r="L639" t="inlineStr">
-        <is>
           <t>Broad tech investments</t>
         </is>
       </c>
@@ -35071,11 +31875,6 @@
       </c>
       <c r="K640" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://khoslaventures.com/team)</t>
-        </is>
-      </c>
-      <c r="L640" s="2" t="inlineStr">
-        <is>
           <t>Deep tech and AI focus</t>
         </is>
       </c>
@@ -35129,11 +31928,6 @@
       </c>
       <c r="K641" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://kleinerperkins.com/people/investors/)</t>
-        </is>
-      </c>
-      <c r="L641" t="inlineStr">
-        <is>
           <t>Historic Silicon Valley firm</t>
         </is>
       </c>
@@ -35187,11 +31981,6 @@
       </c>
       <c r="K642" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://luxcapital.com/people)</t>
-        </is>
-      </c>
-      <c r="L642" s="2" t="inlineStr">
-        <is>
           <t>Emerging science and tech</t>
         </is>
       </c>
@@ -35245,11 +32034,6 @@
       </c>
       <c r="K643" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://greylock.com/team/)</t>
-        </is>
-      </c>
-      <c r="L643" t="inlineStr">
-        <is>
           <t>Enterprise and consumer</t>
         </is>
       </c>
@@ -35303,11 +32087,6 @@
       </c>
       <c r="K644" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://firstround.com/team/)</t>
-        </is>
-      </c>
-      <c r="L644" s="2" t="inlineStr">
-        <is>
           <t>Early stage specialists</t>
         </is>
       </c>
@@ -35361,11 +32140,6 @@
       </c>
       <c r="K645" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://trueventures.com/team)</t>
-        </is>
-      </c>
-      <c r="L645" t="inlineStr">
-        <is>
           <t>Early stage</t>
         </is>
       </c>
@@ -35419,11 +32193,6 @@
       </c>
       <c r="K646" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://www.nea.com/team)</t>
-        </is>
-      </c>
-      <c r="L646" s="2" t="inlineStr">
-        <is>
           <t>Large diversified fund</t>
         </is>
       </c>
@@ -35477,11 +32246,6 @@
       </c>
       <c r="K647" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://www.tigerglobal.com/)</t>
-        </is>
-      </c>
-      <c r="L647" t="inlineStr">
-        <is>
           <t>Growth stage focus</t>
         </is>
       </c>
@@ -35535,11 +32299,6 @@
       </c>
       <c r="K648" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://visionfund.com/team)</t>
-        </is>
-      </c>
-      <c r="L648" s="2" t="inlineStr">
-        <is>
           <t>Massive growth capital</t>
         </is>
       </c>
@@ -35593,11 +32352,6 @@
       </c>
       <c r="K649" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://temasek.com.sg/en/about-us/leadership)</t>
-        </is>
-      </c>
-      <c r="L649" t="inlineStr">
-        <is>
           <t>Singapore state fund</t>
         </is>
       </c>
@@ -35651,11 +32405,6 @@
       </c>
       <c r="K650" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://dst-global.com)</t>
-        </is>
-      </c>
-      <c r="L650" s="2" t="inlineStr">
-        <is>
           <t>Late stage internet</t>
         </is>
       </c>
@@ -35709,11 +32458,6 @@
       </c>
       <c r="K651" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://battery.com/team/)</t>
-        </is>
-      </c>
-      <c r="L651" t="inlineStr">
-        <is>
           <t>Software focus</t>
         </is>
       </c>
@@ -35767,11 +32511,6 @@
       </c>
       <c r="K652" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://insightpartners.com/team/)</t>
-        </is>
-      </c>
-      <c r="L652" s="2" t="inlineStr">
-        <is>
           <t>Scale up capital</t>
         </is>
       </c>
@@ -35825,11 +32564,6 @@
       </c>
       <c r="K653" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://tpg.com/about-us)</t>
-        </is>
-      </c>
-      <c r="L653" t="inlineStr">
-        <is>
           <t>Private equity firm</t>
         </is>
       </c>
@@ -35883,11 +32617,6 @@
       </c>
       <c r="K654" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://silverlake.com/team/)</t>
-        </is>
-      </c>
-      <c r="L654" s="2" t="inlineStr">
-        <is>
           <t>Tech private equity</t>
         </is>
       </c>
@@ -35941,11 +32670,6 @@
       </c>
       <c r="K655" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://coatue.com/privates-portfolio)</t>
-        </is>
-      </c>
-      <c r="L655" t="inlineStr">
-        <is>
           <t>Crossover fund</t>
         </is>
       </c>
@@ -35999,11 +32723,6 @@
       </c>
       <c r="K656" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://p72.vc/team/)</t>
-        </is>
-      </c>
-      <c r="L656" s="2" t="inlineStr">
-        <is>
           <t>AI and Defense focus</t>
         </is>
       </c>
@@ -36057,11 +32776,6 @@
       </c>
       <c r="K657" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://gv.com/team/)</t>
-        </is>
-      </c>
-      <c r="L657" t="inlineStr">
-        <is>
           <t>Alphabet's VC arm</t>
         </is>
       </c>
@@ -36115,11 +32829,6 @@
       </c>
       <c r="K658" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://intelcapital.com/team/)</t>
-        </is>
-      </c>
-      <c r="L658" s="2" t="inlineStr">
-        <is>
           <t>Semiconductor and AI</t>
         </is>
       </c>
@@ -36173,11 +32882,6 @@
       </c>
       <c r="K659" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://salesforceventures.com/team/)</t>
-        </is>
-      </c>
-      <c r="L659" t="inlineStr">
-        <is>
           <t>Enterprise software</t>
         </is>
       </c>
@@ -36231,11 +32935,6 @@
       </c>
       <c r="K660" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://m12.vc/team/)</t>
-        </is>
-      </c>
-      <c r="L660" s="2" t="inlineStr">
-        <is>
           <t>Microsoft's VC arm</t>
         </is>
       </c>
@@ -36289,11 +32988,6 @@
       </c>
       <c r="K661" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://qualcommventures.com/team/)</t>
-        </is>
-      </c>
-      <c r="L661" t="inlineStr">
-        <is>
           <t>Mobile and 5G/AI focus</t>
         </is>
       </c>
@@ -36347,11 +33041,6 @@
       </c>
       <c r="K662" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://samsungnext.com/team/)</t>
-        </is>
-      </c>
-      <c r="L662" s="2" t="inlineStr">
-        <is>
           <t>Samsung's innovation fund</t>
         </is>
       </c>
@@ -36405,11 +33094,6 @@
       </c>
       <c r="K663" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://www.lockheedmartin.com/en-us/who-we-are/leadership-governance.html)</t>
-        </is>
-      </c>
-      <c r="L663" t="inlineStr">
-        <is>
           <t>Defense technology</t>
         </is>
       </c>
@@ -36463,11 +33147,6 @@
       </c>
       <c r="K664" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://www.boeing.com/company/about-bca)</t>
-        </is>
-      </c>
-      <c r="L664" s="2" t="inlineStr">
-        <is>
           <t>Aerospace innovation</t>
         </is>
       </c>
@@ -36521,11 +33200,6 @@
       </c>
       <c r="K665" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://airbusventures.vc/team/)</t>
-        </is>
-      </c>
-      <c r="L665" t="inlineStr">
-        <is>
           <t>Aerospace and deep tech</t>
         </is>
       </c>
@@ -36579,11 +33253,6 @@
       </c>
       <c r="K666" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://rtx.com/who-we-are/leadership)</t>
-        </is>
-      </c>
-      <c r="L666" s="2" t="inlineStr">
-        <is>
           <t>Raytheon's venture arm</t>
         </is>
       </c>
@@ -36637,11 +33306,6 @@
       </c>
       <c r="K667" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://baesystems.com/en/our-company/leadership)</t>
-        </is>
-      </c>
-      <c r="L667" t="inlineStr">
-        <is>
           <t>Defense contractor</t>
         </is>
       </c>
@@ -36695,11 +33359,6 @@
       </c>
       <c r="K668" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://diu.mil/about)</t>
-        </is>
-      </c>
-      <c r="L668" s="2" t="inlineStr">
-        <is>
           <t>Defense Innovation Unit</t>
         </is>
       </c>
@@ -36753,11 +33412,6 @@
       </c>
       <c r="K669" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://darpa.mil/about-us/leadership)</t>
-        </is>
-      </c>
-      <c r="L669" t="inlineStr">
-        <is>
           <t>Advanced defense projects</t>
         </is>
       </c>
@@ -36811,11 +33465,6 @@
       </c>
       <c r="K670" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://afwerx.com/about/)</t>
-        </is>
-      </c>
-      <c r="L670" s="2" t="inlineStr">
-        <is>
           <t>Air Force innovation</t>
         </is>
       </c>
@@ -36869,11 +33518,6 @@
       </c>
       <c r="K671" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://aal.army/about-us/)</t>
-        </is>
-      </c>
-      <c r="L671" t="inlineStr">
-        <is>
           <t>Army modernization</t>
         </is>
       </c>
@@ -36927,11 +33571,6 @@
       </c>
       <c r="K672" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://www.secnav.navy.mil/agility/Pages/about.aspx)</t>
-        </is>
-      </c>
-      <c r="L672" s="2" t="inlineStr">
-        <is>
           <t>Navy innovation</t>
         </is>
       </c>
@@ -36985,11 +33624,6 @@
       </c>
       <c r="K673" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://www.nsic.mil/)</t>
-        </is>
-      </c>
-      <c r="L673" t="inlineStr">
-        <is>
           <t>National Security Innovation Capital</t>
         </is>
       </c>
@@ -37043,11 +33677,6 @@
       </c>
       <c r="K674" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://nif.fund/team/)</t>
-        </is>
-      </c>
-      <c r="L674" s="2" t="inlineStr">
-        <is>
           <t>NATO backed fund</t>
         </is>
       </c>
@@ -37101,11 +33730,6 @@
       </c>
       <c r="K675" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://defence-industry-space.ec.europa.eu/)</t>
-        </is>
-      </c>
-      <c r="L675" t="inlineStr">
-        <is>
           <t>EU defense R&amp;D</t>
         </is>
       </c>
@@ -37159,11 +33783,6 @@
       </c>
       <c r="K676" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://norrsken.vc/about)</t>
-        </is>
-      </c>
-      <c r="L676" s="2" t="inlineStr">
-        <is>
           <t>Impact investing</t>
         </is>
       </c>
@@ -37217,11 +33836,6 @@
       </c>
       <c r="K677" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://cre.vc)</t>
-        </is>
-      </c>
-      <c r="L677" t="inlineStr">
-        <is>
           <t>Sub-Saharan Africa focus</t>
         </is>
       </c>
@@ -37275,11 +33889,6 @@
       </c>
       <c r="K678" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://tlcomcapital.com/team/)</t>
-        </is>
-      </c>
-      <c r="L678" s="2" t="inlineStr">
-        <is>
           <t>African tech ecosystem</t>
         </is>
       </c>
@@ -37333,11 +33942,6 @@
       </c>
       <c r="K679" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://novastarventures.com/team/)</t>
-        </is>
-      </c>
-      <c r="L679" t="inlineStr">
-        <is>
           <t>East and West Africa</t>
         </is>
       </c>
@@ -37391,11 +33995,6 @@
       </c>
       <c r="K680" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://flat6labs.com/about/)</t>
-        </is>
-      </c>
-      <c r="L680" s="2" t="inlineStr">
-        <is>
           <t>MENA region focus</t>
         </is>
       </c>
@@ -37449,11 +34048,6 @@
       </c>
       <c r="K681" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://kaszek.com)</t>
-        </is>
-      </c>
-      <c r="L681" t="inlineStr">
-        <is>
           <t>LatAm ecosystem</t>
         </is>
       </c>
@@ -37507,11 +34101,6 @@
       </c>
       <c r="K682" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://monashees.com.br/team)</t>
-        </is>
-      </c>
-      <c r="L682" s="2" t="inlineStr">
-        <is>
           <t>Website down. Funder may have shut down.</t>
         </is>
       </c>
@@ -37565,11 +34154,6 @@
       </c>
       <c r="K683" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://allvp.com)</t>
-        </is>
-      </c>
-      <c r="L683" t="inlineStr">
-        <is>
           <t>LatAm focus</t>
         </is>
       </c>
@@ -37623,11 +34207,6 @@
       </c>
       <c r="K684" s="2" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://gobi.vc/team/)</t>
-        </is>
-      </c>
-      <c r="L684" s="2" t="inlineStr">
-        <is>
           <t>Pan-Asian VC</t>
         </is>
       </c>
@@ -37681,17 +34260,12 @@
       </c>
       <c r="K685" t="inlineStr">
         <is>
-          <t>[Team/Contact](https://peakxv.com)</t>
-        </is>
-      </c>
-      <c r="L685" t="inlineStr">
-        <is>
           <t>Formerly Sequoia India/SEA</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L685"/>
+  <autoFilter ref="A1:K685"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>